--- a/riobamba-censo-data/shp/plataforma_o.xlsx
+++ b/riobamba-censo-data/shp/plataforma_o.xlsx
@@ -11,7 +11,7 @@
     <sheet name="Datos" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Datos'!$A$1:$J$1</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Datos'!$A$1:$K$1</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -490,7 +490,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J267"/>
+  <dimension ref="A1:K267"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="17" customWidth="1" min="1" max="1"/>
@@ -498,11 +498,12 @@
     <col width="11" customWidth="1" min="3" max="3"/>
     <col width="9" customWidth="1" min="4" max="4"/>
     <col width="9" customWidth="1" min="5" max="5"/>
-    <col width="10" customWidth="1" min="6" max="6"/>
-    <col width="11" customWidth="1" min="7" max="7"/>
+    <col width="9" customWidth="1" min="6" max="6"/>
+    <col width="10" customWidth="1" min="7" max="7"/>
     <col width="11" customWidth="1" min="8" max="8"/>
     <col width="11" customWidth="1" min="9" max="9"/>
     <col width="11" customWidth="1" min="10" max="10"/>
+    <col width="11" customWidth="1" min="11" max="11"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -533,25 +534,30 @@
       </c>
       <c r="F1" s="1" t="inlineStr">
         <is>
-          <t>edad0_14</t>
+          <t>edad0_4</t>
         </is>
       </c>
       <c r="G1" s="1" t="inlineStr">
         <is>
-          <t>edad15_29</t>
+          <t>edad5_11</t>
         </is>
       </c>
       <c r="H1" s="1" t="inlineStr">
         <is>
-          <t>edad30_44</t>
+          <t>edad12_17</t>
         </is>
       </c>
       <c r="I1" s="1" t="inlineStr">
         <is>
-          <t>edad45_64</t>
+          <t>edad18_29</t>
         </is>
       </c>
       <c r="J1" s="1" t="inlineStr">
+        <is>
+          <t>edad30_64</t>
+        </is>
+      </c>
+      <c r="K1" s="1" t="inlineStr">
         <is>
           <t>edad65mas</t>
         </is>
@@ -578,18 +584,21 @@
         <v>21</v>
       </c>
       <c r="F2" t="n">
-        <v>9</v>
+        <v>1</v>
       </c>
       <c r="G2" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="H2" t="n">
-        <v>13</v>
+        <v>4</v>
       </c>
       <c r="I2" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="J2" t="n">
+        <v>17</v>
+      </c>
+      <c r="K2" t="n">
         <v>10</v>
       </c>
     </row>
@@ -614,18 +623,21 @@
         <v>32</v>
       </c>
       <c r="F3" t="n">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="G3" t="n">
-        <v>13</v>
+        <v>1</v>
       </c>
       <c r="H3" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="I3" t="n">
-        <v>19</v>
+        <v>12</v>
       </c>
       <c r="J3" t="n">
+        <v>22</v>
+      </c>
+      <c r="K3" t="n">
         <v>19</v>
       </c>
     </row>
@@ -650,18 +662,21 @@
         <v>46</v>
       </c>
       <c r="F4" t="n">
-        <v>19</v>
+        <v>3</v>
       </c>
       <c r="G4" t="n">
-        <v>18</v>
+        <v>12</v>
       </c>
       <c r="H4" t="n">
-        <v>14</v>
+        <v>7</v>
       </c>
       <c r="I4" t="n">
-        <v>20</v>
+        <v>15</v>
       </c>
       <c r="J4" t="n">
+        <v>34</v>
+      </c>
+      <c r="K4" t="n">
         <v>10</v>
       </c>
     </row>
@@ -686,18 +701,21 @@
         <v>39</v>
       </c>
       <c r="F5" t="n">
+        <v>7</v>
+      </c>
+      <c r="G5" t="n">
+        <v>5</v>
+      </c>
+      <c r="H5" t="n">
+        <v>4</v>
+      </c>
+      <c r="I5" t="n">
         <v>15</v>
       </c>
-      <c r="G5" t="n">
-        <v>16</v>
-      </c>
-      <c r="H5" t="n">
-        <v>18</v>
-      </c>
-      <c r="I5" t="n">
-        <v>11</v>
-      </c>
       <c r="J5" t="n">
+        <v>29</v>
+      </c>
+      <c r="K5" t="n">
         <v>9</v>
       </c>
     </row>
@@ -722,18 +740,21 @@
         <v>33</v>
       </c>
       <c r="F6" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="G6" t="n">
-        <v>12</v>
+        <v>7</v>
       </c>
       <c r="H6" t="n">
-        <v>7</v>
+        <v>2</v>
       </c>
       <c r="I6" t="n">
-        <v>17</v>
+        <v>11</v>
       </c>
       <c r="J6" t="n">
+        <v>24</v>
+      </c>
+      <c r="K6" t="n">
         <v>10</v>
       </c>
     </row>
@@ -758,18 +779,21 @@
         <v>28</v>
       </c>
       <c r="F7" t="n">
-        <v>14</v>
+        <v>5</v>
       </c>
       <c r="G7" t="n">
-        <v>15</v>
+        <v>5</v>
       </c>
       <c r="H7" t="n">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="I7" t="n">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="J7" t="n">
+        <v>20</v>
+      </c>
+      <c r="K7" t="n">
         <v>6</v>
       </c>
     </row>
@@ -794,18 +818,21 @@
         <v>43</v>
       </c>
       <c r="F8" t="n">
-        <v>17</v>
+        <v>4</v>
       </c>
       <c r="G8" t="n">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="H8" t="n">
-        <v>22</v>
+        <v>7</v>
       </c>
       <c r="I8" t="n">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="J8" t="n">
+        <v>34</v>
+      </c>
+      <c r="K8" t="n">
         <v>9</v>
       </c>
     </row>
@@ -830,18 +857,21 @@
         <v>121</v>
       </c>
       <c r="F9" t="n">
-        <v>46</v>
+        <v>11</v>
       </c>
       <c r="G9" t="n">
-        <v>43</v>
+        <v>20</v>
       </c>
       <c r="H9" t="n">
-        <v>50</v>
+        <v>24</v>
       </c>
       <c r="I9" t="n">
-        <v>49</v>
+        <v>34</v>
       </c>
       <c r="J9" t="n">
+        <v>99</v>
+      </c>
+      <c r="K9" t="n">
         <v>34</v>
       </c>
     </row>
@@ -866,18 +896,21 @@
         <v>29</v>
       </c>
       <c r="F10" t="n">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="G10" t="n">
-        <v>16</v>
+        <v>3</v>
       </c>
       <c r="H10" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="I10" t="n">
-        <v>22</v>
+        <v>15</v>
       </c>
       <c r="J10" t="n">
+        <v>30</v>
+      </c>
+      <c r="K10" t="n">
         <v>5</v>
       </c>
     </row>
@@ -902,18 +935,21 @@
         <v>36</v>
       </c>
       <c r="F11" t="n">
-        <v>11</v>
+        <v>1</v>
       </c>
       <c r="G11" t="n">
-        <v>14</v>
+        <v>7</v>
       </c>
       <c r="H11" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="I11" t="n">
-        <v>17</v>
+        <v>12</v>
       </c>
       <c r="J11" t="n">
+        <v>27</v>
+      </c>
+      <c r="K11" t="n">
         <v>9</v>
       </c>
     </row>
@@ -938,18 +974,21 @@
         <v>30</v>
       </c>
       <c r="F12" t="n">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="G12" t="n">
-        <v>13</v>
+        <v>4</v>
       </c>
       <c r="H12" t="n">
-        <v>13</v>
+        <v>3</v>
       </c>
       <c r="I12" t="n">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="J12" t="n">
+        <v>26</v>
+      </c>
+      <c r="K12" t="n">
         <v>4</v>
       </c>
     </row>
@@ -974,18 +1013,21 @@
         <v>28</v>
       </c>
       <c r="F13" t="n">
-        <v>8</v>
+        <v>3</v>
       </c>
       <c r="G13" t="n">
-        <v>11</v>
+        <v>4</v>
       </c>
       <c r="H13" t="n">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="I13" t="n">
-        <v>15</v>
+        <v>9</v>
       </c>
       <c r="J13" t="n">
+        <v>22</v>
+      </c>
+      <c r="K13" t="n">
         <v>2</v>
       </c>
     </row>
@@ -1010,18 +1052,21 @@
         <v>46</v>
       </c>
       <c r="F14" t="n">
-        <v>14</v>
+        <v>2</v>
       </c>
       <c r="G14" t="n">
-        <v>27</v>
+        <v>5</v>
       </c>
       <c r="H14" t="n">
-        <v>19</v>
+        <v>12</v>
       </c>
       <c r="I14" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="J14" t="n">
+        <v>42</v>
+      </c>
+      <c r="K14" t="n">
         <v>12</v>
       </c>
     </row>
@@ -1046,18 +1091,21 @@
         <v>124</v>
       </c>
       <c r="F15" t="n">
-        <v>38</v>
+        <v>9</v>
       </c>
       <c r="G15" t="n">
-        <v>63</v>
+        <v>20</v>
       </c>
       <c r="H15" t="n">
-        <v>43</v>
+        <v>24</v>
       </c>
       <c r="I15" t="n">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="J15" t="n">
+        <v>92</v>
+      </c>
+      <c r="K15" t="n">
         <v>15</v>
       </c>
     </row>
@@ -1082,18 +1130,21 @@
         <v>24</v>
       </c>
       <c r="F16" t="n">
-        <v>11</v>
+        <v>1</v>
       </c>
       <c r="G16" t="n">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="H16" t="n">
-        <v>12</v>
+        <v>5</v>
       </c>
       <c r="I16" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="J16" t="n">
+        <v>22</v>
+      </c>
+      <c r="K16" t="n">
         <v>3</v>
       </c>
     </row>
@@ -1118,18 +1169,21 @@
         <v>17</v>
       </c>
       <c r="F17" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="G17" t="n">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="H17" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="I17" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="J17" t="n">
+        <v>12</v>
+      </c>
+      <c r="K17" t="n">
         <v>6</v>
       </c>
     </row>
@@ -1154,18 +1208,21 @@
         <v>27</v>
       </c>
       <c r="F18" t="n">
-        <v>8</v>
+        <v>3</v>
       </c>
       <c r="G18" t="n">
-        <v>16</v>
+        <v>3</v>
       </c>
       <c r="H18" t="n">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="I18" t="n">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="J18" t="n">
+        <v>24</v>
+      </c>
+      <c r="K18" t="n">
         <v>0</v>
       </c>
     </row>
@@ -1190,18 +1247,21 @@
         <v>32</v>
       </c>
       <c r="F19" t="n">
-        <v>16</v>
+        <v>2</v>
       </c>
       <c r="G19" t="n">
-        <v>14</v>
+        <v>10</v>
       </c>
       <c r="H19" t="n">
-        <v>15</v>
+        <v>9</v>
       </c>
       <c r="I19" t="n">
-        <v>17</v>
+        <v>9</v>
       </c>
       <c r="J19" t="n">
+        <v>32</v>
+      </c>
+      <c r="K19" t="n">
         <v>2</v>
       </c>
     </row>
@@ -1226,18 +1286,21 @@
         <v>109</v>
       </c>
       <c r="F20" t="n">
-        <v>40</v>
+        <v>10</v>
       </c>
       <c r="G20" t="n">
-        <v>57</v>
+        <v>21</v>
       </c>
       <c r="H20" t="n">
-        <v>43</v>
+        <v>18</v>
       </c>
       <c r="I20" t="n">
-        <v>42</v>
+        <v>48</v>
       </c>
       <c r="J20" t="n">
+        <v>85</v>
+      </c>
+      <c r="K20" t="n">
         <v>16</v>
       </c>
     </row>
@@ -1262,18 +1325,21 @@
         <v>31</v>
       </c>
       <c r="F21" t="n">
-        <v>15</v>
+        <v>5</v>
       </c>
       <c r="G21" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="H21" t="n">
-        <v>12</v>
+        <v>6</v>
       </c>
       <c r="I21" t="n">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="J21" t="n">
+        <v>22</v>
+      </c>
+      <c r="K21" t="n">
         <v>12</v>
       </c>
     </row>
@@ -1298,18 +1364,21 @@
         <v>36</v>
       </c>
       <c r="F22" t="n">
-        <v>12</v>
+        <v>1</v>
       </c>
       <c r="G22" t="n">
-        <v>21</v>
+        <v>7</v>
       </c>
       <c r="H22" t="n">
-        <v>15</v>
+        <v>11</v>
       </c>
       <c r="I22" t="n">
-        <v>20</v>
+        <v>14</v>
       </c>
       <c r="J22" t="n">
+        <v>35</v>
+      </c>
+      <c r="K22" t="n">
         <v>9</v>
       </c>
     </row>
@@ -1334,18 +1403,21 @@
         <v>18</v>
       </c>
       <c r="F23" t="n">
-        <v>9</v>
+        <v>1</v>
       </c>
       <c r="G23" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="H23" t="n">
-        <v>13</v>
+        <v>6</v>
       </c>
       <c r="I23" t="n">
-        <v>11</v>
+        <v>4</v>
       </c>
       <c r="J23" t="n">
+        <v>24</v>
+      </c>
+      <c r="K23" t="n">
         <v>2</v>
       </c>
     </row>
@@ -1370,18 +1442,21 @@
         <v>70</v>
       </c>
       <c r="F24" t="n">
-        <v>37</v>
+        <v>13</v>
       </c>
       <c r="G24" t="n">
-        <v>30</v>
+        <v>20</v>
       </c>
       <c r="H24" t="n">
+        <v>9</v>
+      </c>
+      <c r="I24" t="n">
         <v>25</v>
       </c>
-      <c r="I24" t="n">
-        <v>14</v>
-      </c>
       <c r="J24" t="n">
+        <v>39</v>
+      </c>
+      <c r="K24" t="n">
         <v>5</v>
       </c>
     </row>
@@ -1406,18 +1481,21 @@
         <v>51</v>
       </c>
       <c r="F25" t="n">
-        <v>21</v>
+        <v>3</v>
       </c>
       <c r="G25" t="n">
-        <v>30</v>
+        <v>7</v>
       </c>
       <c r="H25" t="n">
-        <v>27</v>
+        <v>15</v>
       </c>
       <c r="I25" t="n">
-        <v>17</v>
+        <v>26</v>
       </c>
       <c r="J25" t="n">
+        <v>44</v>
+      </c>
+      <c r="K25" t="n">
         <v>7</v>
       </c>
     </row>
@@ -1442,18 +1520,21 @@
         <v>25</v>
       </c>
       <c r="F26" t="n">
-        <v>15</v>
+        <v>5</v>
       </c>
       <c r="G26" t="n">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="H26" t="n">
-        <v>8</v>
+        <v>3</v>
       </c>
       <c r="I26" t="n">
-        <v>4</v>
+        <v>9</v>
       </c>
       <c r="J26" t="n">
+        <v>12</v>
+      </c>
+      <c r="K26" t="n">
         <v>2</v>
       </c>
     </row>
@@ -1478,18 +1559,21 @@
         <v>37</v>
       </c>
       <c r="F27" t="n">
-        <v>17</v>
+        <v>4</v>
       </c>
       <c r="G27" t="n">
-        <v>16</v>
+        <v>9</v>
       </c>
       <c r="H27" t="n">
-        <v>21</v>
+        <v>8</v>
       </c>
       <c r="I27" t="n">
         <v>12</v>
       </c>
       <c r="J27" t="n">
+        <v>33</v>
+      </c>
+      <c r="K27" t="n">
         <v>8</v>
       </c>
     </row>
@@ -1514,18 +1598,21 @@
         <v>46</v>
       </c>
       <c r="F28" t="n">
-        <v>21</v>
+        <v>7</v>
       </c>
       <c r="G28" t="n">
-        <v>16</v>
+        <v>10</v>
       </c>
       <c r="H28" t="n">
-        <v>23</v>
+        <v>6</v>
       </c>
       <c r="I28" t="n">
-        <v>20</v>
+        <v>14</v>
       </c>
       <c r="J28" t="n">
+        <v>43</v>
+      </c>
+      <c r="K28" t="n">
         <v>6</v>
       </c>
     </row>
@@ -1550,18 +1637,21 @@
         <v>21</v>
       </c>
       <c r="F29" t="n">
-        <v>8</v>
+        <v>1</v>
       </c>
       <c r="G29" t="n">
-        <v>15</v>
+        <v>4</v>
       </c>
       <c r="H29" t="n">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="I29" t="n">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="J29" t="n">
+        <v>19</v>
+      </c>
+      <c r="K29" t="n">
         <v>0</v>
       </c>
     </row>
@@ -1586,18 +1676,21 @@
         <v>9</v>
       </c>
       <c r="F30" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="G30" t="n">
+        <v>5</v>
+      </c>
+      <c r="H30" t="n">
+        <v>0</v>
+      </c>
+      <c r="I30" t="n">
         <v>10</v>
       </c>
-      <c r="H30" t="n">
-        <v>3</v>
-      </c>
-      <c r="I30" t="n">
-        <v>5</v>
-      </c>
       <c r="J30" t="n">
+        <v>8</v>
+      </c>
+      <c r="K30" t="n">
         <v>1</v>
       </c>
     </row>
@@ -1622,18 +1715,21 @@
         <v>32</v>
       </c>
       <c r="F31" t="n">
-        <v>12</v>
+        <v>4</v>
       </c>
       <c r="G31" t="n">
-        <v>15</v>
+        <v>5</v>
       </c>
       <c r="H31" t="n">
         <v>7</v>
       </c>
       <c r="I31" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="J31" t="n">
+        <v>19</v>
+      </c>
+      <c r="K31" t="n">
         <v>8</v>
       </c>
     </row>
@@ -1658,18 +1754,21 @@
         <v>61</v>
       </c>
       <c r="F32" t="n">
-        <v>24</v>
+        <v>8</v>
       </c>
       <c r="G32" t="n">
-        <v>32</v>
+        <v>12</v>
       </c>
       <c r="H32" t="n">
-        <v>20</v>
+        <v>8</v>
       </c>
       <c r="I32" t="n">
-        <v>32</v>
+        <v>28</v>
       </c>
       <c r="J32" t="n">
+        <v>52</v>
+      </c>
+      <c r="K32" t="n">
         <v>8</v>
       </c>
     </row>
@@ -1694,18 +1793,21 @@
         <v>51</v>
       </c>
       <c r="F33" t="n">
-        <v>12</v>
+        <v>3</v>
       </c>
       <c r="G33" t="n">
-        <v>27</v>
+        <v>6</v>
       </c>
       <c r="H33" t="n">
-        <v>16</v>
+        <v>10</v>
       </c>
       <c r="I33" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="J33" t="n">
+        <v>37</v>
+      </c>
+      <c r="K33" t="n">
         <v>6</v>
       </c>
     </row>
@@ -1730,18 +1832,21 @@
         <v>29</v>
       </c>
       <c r="F34" t="n">
-        <v>7</v>
+        <v>2</v>
       </c>
       <c r="G34" t="n">
+        <v>4</v>
+      </c>
+      <c r="H34" t="n">
+        <v>1</v>
+      </c>
+      <c r="I34" t="n">
         <v>9</v>
       </c>
-      <c r="H34" t="n">
-        <v>18</v>
-      </c>
-      <c r="I34" t="n">
-        <v>18</v>
-      </c>
       <c r="J34" t="n">
+        <v>36</v>
+      </c>
+      <c r="K34" t="n">
         <v>9</v>
       </c>
     </row>
@@ -1766,18 +1871,21 @@
         <v>49</v>
       </c>
       <c r="F35" t="n">
-        <v>16</v>
+        <v>6</v>
       </c>
       <c r="G35" t="n">
-        <v>23</v>
+        <v>7</v>
       </c>
       <c r="H35" t="n">
-        <v>23</v>
+        <v>7</v>
       </c>
       <c r="I35" t="n">
         <v>19</v>
       </c>
       <c r="J35" t="n">
+        <v>42</v>
+      </c>
+      <c r="K35" t="n">
         <v>7</v>
       </c>
     </row>
@@ -1802,18 +1910,21 @@
         <v>37</v>
       </c>
       <c r="F36" t="n">
-        <v>17</v>
+        <v>3</v>
       </c>
       <c r="G36" t="n">
-        <v>21</v>
+        <v>10</v>
       </c>
       <c r="H36" t="n">
-        <v>17</v>
+        <v>6</v>
       </c>
       <c r="I36" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="J36" t="n">
+        <v>35</v>
+      </c>
+      <c r="K36" t="n">
         <v>6</v>
       </c>
     </row>
@@ -1838,18 +1949,21 @@
         <v>24</v>
       </c>
       <c r="F37" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="G37" t="n">
-        <v>10</v>
+        <v>3</v>
       </c>
       <c r="H37" t="n">
-        <v>11</v>
+        <v>6</v>
       </c>
       <c r="I37" t="n">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="J37" t="n">
+        <v>19</v>
+      </c>
+      <c r="K37" t="n">
         <v>14</v>
       </c>
     </row>
@@ -1874,18 +1988,21 @@
         <v>24</v>
       </c>
       <c r="F38" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="G38" t="n">
-        <v>12</v>
+        <v>1</v>
       </c>
       <c r="H38" t="n">
-        <v>14</v>
+        <v>4</v>
       </c>
       <c r="I38" t="n">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="J38" t="n">
+        <v>20</v>
+      </c>
+      <c r="K38" t="n">
         <v>11</v>
       </c>
     </row>
@@ -1910,18 +2027,21 @@
         <v>18</v>
       </c>
       <c r="F39" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="G39" t="n">
-        <v>9</v>
+        <v>3</v>
       </c>
       <c r="H39" t="n">
-        <v>10</v>
+        <v>3</v>
       </c>
       <c r="I39" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="J39" t="n">
+        <v>18</v>
+      </c>
+      <c r="K39" t="n">
         <v>9</v>
       </c>
     </row>
@@ -1946,18 +2066,21 @@
         <v>21</v>
       </c>
       <c r="F40" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="G40" t="n">
-        <v>10</v>
+        <v>2</v>
       </c>
       <c r="H40" t="n">
-        <v>11</v>
+        <v>7</v>
       </c>
       <c r="I40" t="n">
         <v>7</v>
       </c>
       <c r="J40" t="n">
+        <v>18</v>
+      </c>
+      <c r="K40" t="n">
         <v>3</v>
       </c>
     </row>
@@ -1982,18 +2105,21 @@
         <v>32</v>
       </c>
       <c r="F41" t="n">
-        <v>13</v>
+        <v>4</v>
       </c>
       <c r="G41" t="n">
-        <v>12</v>
+        <v>6</v>
       </c>
       <c r="H41" t="n">
-        <v>11</v>
+        <v>5</v>
       </c>
       <c r="I41" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="J41" t="n">
+        <v>26</v>
+      </c>
+      <c r="K41" t="n">
         <v>11</v>
       </c>
     </row>
@@ -2018,18 +2144,21 @@
         <v>24</v>
       </c>
       <c r="F42" t="n">
-        <v>10</v>
+        <v>2</v>
       </c>
       <c r="G42" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="H42" t="n">
-        <v>17</v>
+        <v>5</v>
       </c>
       <c r="I42" t="n">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="J42" t="n">
+        <v>25</v>
+      </c>
+      <c r="K42" t="n">
         <v>6</v>
       </c>
     </row>
@@ -2054,18 +2183,21 @@
         <v>86</v>
       </c>
       <c r="F43" t="n">
-        <v>35</v>
+        <v>8</v>
       </c>
       <c r="G43" t="n">
-        <v>34</v>
+        <v>20</v>
       </c>
       <c r="H43" t="n">
-        <v>36</v>
+        <v>12</v>
       </c>
       <c r="I43" t="n">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="J43" t="n">
+        <v>66</v>
+      </c>
+      <c r="K43" t="n">
         <v>26</v>
       </c>
     </row>
@@ -2090,18 +2222,21 @@
         <v>20</v>
       </c>
       <c r="F44" t="n">
+        <v>2</v>
+      </c>
+      <c r="G44" t="n">
+        <v>3</v>
+      </c>
+      <c r="H44" t="n">
         <v>7</v>
       </c>
-      <c r="G44" t="n">
-        <v>9</v>
-      </c>
-      <c r="H44" t="n">
-        <v>18</v>
-      </c>
       <c r="I44" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="J44" t="n">
+        <v>21</v>
+      </c>
+      <c r="K44" t="n">
         <v>0</v>
       </c>
     </row>
@@ -2126,18 +2261,21 @@
         <v>21</v>
       </c>
       <c r="F45" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="G45" t="n">
-        <v>11</v>
+        <v>2</v>
       </c>
       <c r="H45" t="n">
-        <v>9</v>
+        <v>3</v>
       </c>
       <c r="I45" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="J45" t="n">
+        <v>16</v>
+      </c>
+      <c r="K45" t="n">
         <v>3</v>
       </c>
     </row>
@@ -2162,18 +2300,21 @@
         <v>40</v>
       </c>
       <c r="F46" t="n">
-        <v>20</v>
+        <v>5</v>
       </c>
       <c r="G46" t="n">
-        <v>22</v>
+        <v>11</v>
       </c>
       <c r="H46" t="n">
-        <v>16</v>
+        <v>8</v>
       </c>
       <c r="I46" t="n">
-        <v>12</v>
+        <v>18</v>
       </c>
       <c r="J46" t="n">
+        <v>28</v>
+      </c>
+      <c r="K46" t="n">
         <v>2</v>
       </c>
     </row>
@@ -2198,18 +2339,21 @@
         <v>7</v>
       </c>
       <c r="F47" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="G47" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="H47" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="I47" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="J47" t="n">
+        <v>8</v>
+      </c>
+      <c r="K47" t="n">
         <v>0</v>
       </c>
     </row>
@@ -2234,18 +2378,21 @@
         <v>34</v>
       </c>
       <c r="F48" t="n">
-        <v>13</v>
+        <v>6</v>
       </c>
       <c r="G48" t="n">
-        <v>17</v>
+        <v>6</v>
       </c>
       <c r="H48" t="n">
-        <v>19</v>
+        <v>6</v>
       </c>
       <c r="I48" t="n">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="J48" t="n">
+        <v>28</v>
+      </c>
+      <c r="K48" t="n">
         <v>2</v>
       </c>
     </row>
@@ -2270,18 +2417,21 @@
         <v>15</v>
       </c>
       <c r="F49" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G49" t="n">
-        <v>9</v>
+        <v>1</v>
       </c>
       <c r="H49" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="I49" t="n">
-        <v>13</v>
+        <v>5</v>
       </c>
       <c r="J49" t="n">
+        <v>18</v>
+      </c>
+      <c r="K49" t="n">
         <v>3</v>
       </c>
     </row>
@@ -2306,18 +2456,21 @@
         <v>32</v>
       </c>
       <c r="F50" t="n">
-        <v>17</v>
+        <v>3</v>
       </c>
       <c r="G50" t="n">
         <v>11</v>
       </c>
       <c r="H50" t="n">
-        <v>13</v>
+        <v>4</v>
       </c>
       <c r="I50" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="J50" t="n">
+        <v>24</v>
+      </c>
+      <c r="K50" t="n">
         <v>3</v>
       </c>
     </row>
@@ -2342,18 +2495,21 @@
         <v>24</v>
       </c>
       <c r="F51" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="G51" t="n">
-        <v>19</v>
+        <v>2</v>
       </c>
       <c r="H51" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="I51" t="n">
-        <v>7</v>
+        <v>15</v>
       </c>
       <c r="J51" t="n">
+        <v>13</v>
+      </c>
+      <c r="K51" t="n">
         <v>6</v>
       </c>
     </row>
@@ -2378,18 +2534,21 @@
         <v>53</v>
       </c>
       <c r="F52" t="n">
-        <v>17</v>
+        <v>1</v>
       </c>
       <c r="G52" t="n">
-        <v>20</v>
+        <v>11</v>
       </c>
       <c r="H52" t="n">
-        <v>23</v>
+        <v>11</v>
       </c>
       <c r="I52" t="n">
-        <v>26</v>
+        <v>14</v>
       </c>
       <c r="J52" t="n">
+        <v>49</v>
+      </c>
+      <c r="K52" t="n">
         <v>11</v>
       </c>
     </row>
@@ -2414,18 +2573,21 @@
         <v>28</v>
       </c>
       <c r="F53" t="n">
-        <v>13</v>
+        <v>3</v>
       </c>
       <c r="G53" t="n">
-        <v>13</v>
+        <v>7</v>
       </c>
       <c r="H53" t="n">
-        <v>13</v>
+        <v>5</v>
       </c>
       <c r="I53" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="J53" t="n">
+        <v>23</v>
+      </c>
+      <c r="K53" t="n">
         <v>5</v>
       </c>
     </row>
@@ -2450,18 +2612,21 @@
         <v>20</v>
       </c>
       <c r="F54" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G54" t="n">
-        <v>12</v>
+        <v>1</v>
       </c>
       <c r="H54" t="n">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="I54" t="n">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="J54" t="n">
+        <v>14</v>
+      </c>
+      <c r="K54" t="n">
         <v>4</v>
       </c>
     </row>
@@ -2486,18 +2651,21 @@
         <v>63</v>
       </c>
       <c r="F55" t="n">
-        <v>27</v>
+        <v>9</v>
       </c>
       <c r="G55" t="n">
-        <v>26</v>
+        <v>12</v>
       </c>
       <c r="H55" t="n">
-        <v>24</v>
+        <v>10</v>
       </c>
       <c r="I55" t="n">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="J55" t="n">
+        <v>48</v>
+      </c>
+      <c r="K55" t="n">
         <v>3</v>
       </c>
     </row>
@@ -2522,18 +2690,21 @@
         <v>22</v>
       </c>
       <c r="F56" t="n">
-        <v>13</v>
+        <v>6</v>
       </c>
       <c r="G56" t="n">
-        <v>12</v>
+        <v>4</v>
       </c>
       <c r="H56" t="n">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="I56" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="J56" t="n">
+        <v>18</v>
+      </c>
+      <c r="K56" t="n">
         <v>6</v>
       </c>
     </row>
@@ -2558,18 +2729,21 @@
         <v>20</v>
       </c>
       <c r="F57" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="G57" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="H57" t="n">
-        <v>7</v>
+        <v>1</v>
       </c>
       <c r="I57" t="n">
-        <v>10</v>
+        <v>3</v>
       </c>
       <c r="J57" t="n">
+        <v>17</v>
+      </c>
+      <c r="K57" t="n">
         <v>7</v>
       </c>
     </row>
@@ -2594,18 +2768,21 @@
         <v>19</v>
       </c>
       <c r="F58" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G58" t="n">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="H58" t="n">
         <v>4</v>
       </c>
       <c r="I58" t="n">
-        <v>12</v>
+        <v>7</v>
       </c>
       <c r="J58" t="n">
+        <v>16</v>
+      </c>
+      <c r="K58" t="n">
         <v>5</v>
       </c>
     </row>
@@ -2630,18 +2807,21 @@
         <v>18</v>
       </c>
       <c r="F59" t="n">
+        <v>0</v>
+      </c>
+      <c r="G59" t="n">
         <v>2</v>
       </c>
-      <c r="G59" t="n">
-        <v>8</v>
-      </c>
       <c r="H59" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="I59" t="n">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="J59" t="n">
+        <v>14</v>
+      </c>
+      <c r="K59" t="n">
         <v>7</v>
       </c>
     </row>
@@ -2666,18 +2846,21 @@
         <v>24</v>
       </c>
       <c r="F60" t="n">
-        <v>15</v>
+        <v>6</v>
       </c>
       <c r="G60" t="n">
+        <v>4</v>
+      </c>
+      <c r="H60" t="n">
+        <v>5</v>
+      </c>
+      <c r="I60" t="n">
         <v>12</v>
       </c>
-      <c r="H60" t="n">
-        <v>8</v>
-      </c>
-      <c r="I60" t="n">
-        <v>10</v>
-      </c>
       <c r="J60" t="n">
+        <v>18</v>
+      </c>
+      <c r="K60" t="n">
         <v>0</v>
       </c>
     </row>
@@ -2702,18 +2885,21 @@
         <v>134</v>
       </c>
       <c r="F61" t="n">
-        <v>72</v>
+        <v>15</v>
       </c>
       <c r="G61" t="n">
-        <v>76</v>
+        <v>38</v>
       </c>
       <c r="H61" t="n">
-        <v>49</v>
+        <v>37</v>
       </c>
       <c r="I61" t="n">
-        <v>48</v>
+        <v>58</v>
       </c>
       <c r="J61" t="n">
+        <v>97</v>
+      </c>
+      <c r="K61" t="n">
         <v>13</v>
       </c>
     </row>
@@ -2738,18 +2924,21 @@
         <v>5</v>
       </c>
       <c r="F62" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G62" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="H62" t="n">
         <v>2</v>
       </c>
       <c r="I62" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="J62" t="n">
+        <v>7</v>
+      </c>
+      <c r="K62" t="n">
         <v>1</v>
       </c>
     </row>
@@ -2774,18 +2963,21 @@
         <v>26</v>
       </c>
       <c r="F63" t="n">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="G63" t="n">
-        <v>13</v>
+        <v>6</v>
       </c>
       <c r="H63" t="n">
-        <v>17</v>
+        <v>4</v>
       </c>
       <c r="I63" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="J63" t="n">
+        <v>30</v>
+      </c>
+      <c r="K63" t="n">
         <v>4</v>
       </c>
     </row>
@@ -2810,18 +3002,21 @@
         <v>27</v>
       </c>
       <c r="F64" t="n">
-        <v>10</v>
+        <v>3</v>
       </c>
       <c r="G64" t="n">
-        <v>13</v>
+        <v>4</v>
       </c>
       <c r="H64" t="n">
-        <v>12</v>
+        <v>7</v>
       </c>
       <c r="I64" t="n">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="J64" t="n">
+        <v>24</v>
+      </c>
+      <c r="K64" t="n">
         <v>2</v>
       </c>
     </row>
@@ -2846,18 +3041,21 @@
         <v>34</v>
       </c>
       <c r="F65" t="n">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="G65" t="n">
-        <v>18</v>
+        <v>6</v>
       </c>
       <c r="H65" t="n">
+        <v>9</v>
+      </c>
+      <c r="I65" t="n">
         <v>13</v>
       </c>
-      <c r="I65" t="n">
-        <v>12</v>
-      </c>
       <c r="J65" t="n">
+        <v>25</v>
+      </c>
+      <c r="K65" t="n">
         <v>7</v>
       </c>
     </row>
@@ -2882,18 +3080,21 @@
         <v>26</v>
       </c>
       <c r="F66" t="n">
+        <v>3</v>
+      </c>
+      <c r="G66" t="n">
+        <v>3</v>
+      </c>
+      <c r="H66" t="n">
         <v>9</v>
       </c>
-      <c r="G66" t="n">
-        <v>17</v>
-      </c>
-      <c r="H66" t="n">
-        <v>12</v>
-      </c>
       <c r="I66" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="J66" t="n">
+        <v>22</v>
+      </c>
+      <c r="K66" t="n">
         <v>1</v>
       </c>
     </row>
@@ -2918,18 +3119,21 @@
         <v>16</v>
       </c>
       <c r="F67" t="n">
-        <v>9</v>
+        <v>2</v>
       </c>
       <c r="G67" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="H67" t="n">
-        <v>9</v>
+        <v>4</v>
       </c>
       <c r="I67" t="n">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="J67" t="n">
+        <v>17</v>
+      </c>
+      <c r="K67" t="n">
         <v>1</v>
       </c>
     </row>
@@ -2954,18 +3158,21 @@
         <v>30</v>
       </c>
       <c r="F68" t="n">
-        <v>17</v>
+        <v>7</v>
       </c>
       <c r="G68" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="H68" t="n">
-        <v>26</v>
+        <v>4</v>
       </c>
       <c r="I68" t="n">
-        <v>11</v>
+        <v>5</v>
       </c>
       <c r="J68" t="n">
+        <v>37</v>
+      </c>
+      <c r="K68" t="n">
         <v>4</v>
       </c>
     </row>
@@ -2990,18 +3197,21 @@
         <v>48</v>
       </c>
       <c r="F69" t="n">
-        <v>20</v>
+        <v>4</v>
       </c>
       <c r="G69" t="n">
-        <v>16</v>
+        <v>9</v>
       </c>
       <c r="H69" t="n">
-        <v>20</v>
+        <v>12</v>
       </c>
       <c r="I69" t="n">
-        <v>18</v>
+        <v>11</v>
       </c>
       <c r="J69" t="n">
+        <v>38</v>
+      </c>
+      <c r="K69" t="n">
         <v>6</v>
       </c>
     </row>
@@ -3026,18 +3236,21 @@
         <v>40</v>
       </c>
       <c r="F70" t="n">
-        <v>13</v>
+        <v>3</v>
       </c>
       <c r="G70" t="n">
-        <v>19</v>
+        <v>5</v>
       </c>
       <c r="H70" t="n">
+        <v>8</v>
+      </c>
+      <c r="I70" t="n">
         <v>16</v>
       </c>
-      <c r="I70" t="n">
-        <v>17</v>
-      </c>
       <c r="J70" t="n">
+        <v>33</v>
+      </c>
+      <c r="K70" t="n">
         <v>3</v>
       </c>
     </row>
@@ -3062,18 +3275,21 @@
         <v>32</v>
       </c>
       <c r="F71" t="n">
-        <v>13</v>
+        <v>1</v>
       </c>
       <c r="G71" t="n">
-        <v>18</v>
+        <v>8</v>
       </c>
       <c r="H71" t="n">
+        <v>8</v>
+      </c>
+      <c r="I71" t="n">
         <v>14</v>
       </c>
-      <c r="I71" t="n">
-        <v>15</v>
-      </c>
       <c r="J71" t="n">
+        <v>29</v>
+      </c>
+      <c r="K71" t="n">
         <v>4</v>
       </c>
     </row>
@@ -3098,18 +3314,21 @@
         <v>31</v>
       </c>
       <c r="F72" t="n">
-        <v>10</v>
+        <v>2</v>
       </c>
       <c r="G72" t="n">
-        <v>20</v>
+        <v>6</v>
       </c>
       <c r="H72" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="I72" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="J72" t="n">
+        <v>23</v>
+      </c>
+      <c r="K72" t="n">
         <v>8</v>
       </c>
     </row>
@@ -3134,18 +3353,21 @@
         <v>20</v>
       </c>
       <c r="F73" t="n">
-        <v>10</v>
+        <v>3</v>
       </c>
       <c r="G73" t="n">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="H73" t="n">
-        <v>7</v>
+        <v>2</v>
       </c>
       <c r="I73" t="n">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="J73" t="n">
+        <v>11</v>
+      </c>
+      <c r="K73" t="n">
         <v>0</v>
       </c>
     </row>
@@ -3170,18 +3392,21 @@
         <v>37</v>
       </c>
       <c r="F74" t="n">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="G74" t="n">
-        <v>13</v>
+        <v>2</v>
       </c>
       <c r="H74" t="n">
-        <v>10</v>
+        <v>3</v>
       </c>
       <c r="I74" t="n">
-        <v>28</v>
+        <v>12</v>
       </c>
       <c r="J74" t="n">
+        <v>38</v>
+      </c>
+      <c r="K74" t="n">
         <v>10</v>
       </c>
     </row>
@@ -3206,18 +3431,21 @@
         <v>52</v>
       </c>
       <c r="F75" t="n">
-        <v>12</v>
+        <v>5</v>
       </c>
       <c r="G75" t="n">
-        <v>21</v>
+        <v>5</v>
       </c>
       <c r="H75" t="n">
-        <v>12</v>
+        <v>4</v>
       </c>
       <c r="I75" t="n">
-        <v>25</v>
+        <v>19</v>
       </c>
       <c r="J75" t="n">
+        <v>37</v>
+      </c>
+      <c r="K75" t="n">
         <v>19</v>
       </c>
     </row>
@@ -3242,18 +3470,21 @@
         <v>57</v>
       </c>
       <c r="F76" t="n">
-        <v>20</v>
+        <v>8</v>
       </c>
       <c r="G76" t="n">
-        <v>25</v>
+        <v>5</v>
       </c>
       <c r="H76" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="I76" t="n">
         <v>22</v>
       </c>
       <c r="J76" t="n">
+        <v>47</v>
+      </c>
+      <c r="K76" t="n">
         <v>12</v>
       </c>
     </row>
@@ -3290,6 +3521,9 @@
         <v>0</v>
       </c>
       <c r="J77" t="n">
+        <v>0</v>
+      </c>
+      <c r="K77" t="n">
         <v>2</v>
       </c>
     </row>
@@ -3314,18 +3548,21 @@
         <v>30</v>
       </c>
       <c r="F78" t="n">
-        <v>14</v>
+        <v>3</v>
       </c>
       <c r="G78" t="n">
-        <v>13</v>
+        <v>6</v>
       </c>
       <c r="H78" t="n">
+        <v>6</v>
+      </c>
+      <c r="I78" t="n">
         <v>12</v>
       </c>
-      <c r="I78" t="n">
-        <v>15</v>
-      </c>
       <c r="J78" t="n">
+        <v>27</v>
+      </c>
+      <c r="K78" t="n">
         <v>8</v>
       </c>
     </row>
@@ -3350,18 +3587,21 @@
         <v>27</v>
       </c>
       <c r="F79" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="G79" t="n">
-        <v>17</v>
+        <v>0</v>
       </c>
       <c r="H79" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="I79" t="n">
-        <v>18</v>
+        <v>12</v>
       </c>
       <c r="J79" t="n">
+        <v>24</v>
+      </c>
+      <c r="K79" t="n">
         <v>9</v>
       </c>
     </row>
@@ -3386,18 +3626,21 @@
         <v>45</v>
       </c>
       <c r="F80" t="n">
-        <v>19</v>
+        <v>6</v>
       </c>
       <c r="G80" t="n">
-        <v>11</v>
+        <v>5</v>
       </c>
       <c r="H80" t="n">
-        <v>21</v>
+        <v>10</v>
       </c>
       <c r="I80" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="J80" t="n">
+        <v>31</v>
+      </c>
+      <c r="K80" t="n">
         <v>13</v>
       </c>
     </row>
@@ -3422,18 +3665,21 @@
         <v>43</v>
       </c>
       <c r="F81" t="n">
-        <v>10</v>
+        <v>3</v>
       </c>
       <c r="G81" t="n">
-        <v>21</v>
+        <v>6</v>
       </c>
       <c r="H81" t="n">
-        <v>20</v>
+        <v>7</v>
       </c>
       <c r="I81" t="n">
         <v>15</v>
       </c>
       <c r="J81" t="n">
+        <v>35</v>
+      </c>
+      <c r="K81" t="n">
         <v>9</v>
       </c>
     </row>
@@ -3458,18 +3704,21 @@
         <v>35</v>
       </c>
       <c r="F82" t="n">
-        <v>15</v>
+        <v>2</v>
       </c>
       <c r="G82" t="n">
-        <v>15</v>
+        <v>8</v>
       </c>
       <c r="H82" t="n">
-        <v>13</v>
+        <v>6</v>
       </c>
       <c r="I82" t="n">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="J82" t="n">
+        <v>24</v>
+      </c>
+      <c r="K82" t="n">
         <v>13</v>
       </c>
     </row>
@@ -3494,18 +3743,21 @@
         <v>41</v>
       </c>
       <c r="F83" t="n">
-        <v>18</v>
+        <v>6</v>
       </c>
       <c r="G83" t="n">
-        <v>14</v>
+        <v>10</v>
       </c>
       <c r="H83" t="n">
-        <v>17</v>
+        <v>4</v>
       </c>
       <c r="I83" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="J83" t="n">
+        <v>30</v>
+      </c>
+      <c r="K83" t="n">
         <v>7</v>
       </c>
     </row>
@@ -3530,18 +3782,21 @@
         <v>61</v>
       </c>
       <c r="F84" t="n">
-        <v>31</v>
+        <v>7</v>
       </c>
       <c r="G84" t="n">
-        <v>35</v>
+        <v>15</v>
       </c>
       <c r="H84" t="n">
-        <v>31</v>
+        <v>20</v>
       </c>
       <c r="I84" t="n">
-        <v>18</v>
+        <v>24</v>
       </c>
       <c r="J84" t="n">
+        <v>49</v>
+      </c>
+      <c r="K84" t="n">
         <v>8</v>
       </c>
     </row>
@@ -3566,18 +3821,21 @@
         <v>93</v>
       </c>
       <c r="F85" t="n">
+        <v>12</v>
+      </c>
+      <c r="G85" t="n">
+        <v>17</v>
+      </c>
+      <c r="H85" t="n">
+        <v>17</v>
+      </c>
+      <c r="I85" t="n">
         <v>41</v>
       </c>
-      <c r="G85" t="n">
-        <v>46</v>
-      </c>
-      <c r="H85" t="n">
-        <v>42</v>
-      </c>
-      <c r="I85" t="n">
-        <v>28</v>
-      </c>
       <c r="J85" t="n">
+        <v>70</v>
+      </c>
+      <c r="K85" t="n">
         <v>13</v>
       </c>
     </row>
@@ -3602,18 +3860,21 @@
         <v>36</v>
       </c>
       <c r="F86" t="n">
-        <v>20</v>
+        <v>5</v>
       </c>
       <c r="G86" t="n">
-        <v>26</v>
+        <v>10</v>
       </c>
       <c r="H86" t="n">
-        <v>20</v>
+        <v>12</v>
       </c>
       <c r="I86" t="n">
-        <v>9</v>
+        <v>19</v>
       </c>
       <c r="J86" t="n">
+        <v>29</v>
+      </c>
+      <c r="K86" t="n">
         <v>10</v>
       </c>
     </row>
@@ -3638,18 +3899,21 @@
         <v>50</v>
       </c>
       <c r="F87" t="n">
-        <v>18</v>
+        <v>5</v>
       </c>
       <c r="G87" t="n">
-        <v>31</v>
+        <v>10</v>
       </c>
       <c r="H87" t="n">
-        <v>23</v>
+        <v>12</v>
       </c>
       <c r="I87" t="n">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="J87" t="n">
+        <v>47</v>
+      </c>
+      <c r="K87" t="n">
         <v>10</v>
       </c>
     </row>
@@ -3674,18 +3938,21 @@
         <v>32</v>
       </c>
       <c r="F88" t="n">
-        <v>14</v>
+        <v>6</v>
       </c>
       <c r="G88" t="n">
+        <v>5</v>
+      </c>
+      <c r="H88" t="n">
+        <v>3</v>
+      </c>
+      <c r="I88" t="n">
         <v>8</v>
       </c>
-      <c r="H88" t="n">
-        <v>14</v>
-      </c>
-      <c r="I88" t="n">
-        <v>12</v>
-      </c>
       <c r="J88" t="n">
+        <v>26</v>
+      </c>
+      <c r="K88" t="n">
         <v>5</v>
       </c>
     </row>
@@ -3710,18 +3977,21 @@
         <v>22</v>
       </c>
       <c r="F89" t="n">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="G89" t="n">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="H89" t="n">
-        <v>12</v>
+        <v>4</v>
       </c>
       <c r="I89" t="n">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="J89" t="n">
+        <v>20</v>
+      </c>
+      <c r="K89" t="n">
         <v>4</v>
       </c>
     </row>
@@ -3746,18 +4016,21 @@
         <v>15</v>
       </c>
       <c r="F90" t="n">
-        <v>7</v>
+        <v>1</v>
       </c>
       <c r="G90" t="n">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="H90" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="I90" t="n">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="J90" t="n">
+        <v>13</v>
+      </c>
+      <c r="K90" t="n">
         <v>0</v>
       </c>
     </row>
@@ -3782,18 +4055,21 @@
         <v>11</v>
       </c>
       <c r="F91" t="n">
+        <v>0</v>
+      </c>
+      <c r="G91" t="n">
         <v>2</v>
       </c>
-      <c r="G91" t="n">
-        <v>4</v>
-      </c>
       <c r="H91" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="I91" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="J91" t="n">
+        <v>10</v>
+      </c>
+      <c r="K91" t="n">
         <v>3</v>
       </c>
     </row>
@@ -3818,18 +4094,21 @@
         <v>47</v>
       </c>
       <c r="F92" t="n">
-        <v>14</v>
+        <v>4</v>
       </c>
       <c r="G92" t="n">
-        <v>25</v>
+        <v>7</v>
       </c>
       <c r="H92" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="I92" t="n">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="J92" t="n">
+        <v>40</v>
+      </c>
+      <c r="K92" t="n">
         <v>8</v>
       </c>
     </row>
@@ -3857,15 +4136,18 @@
         <v>0</v>
       </c>
       <c r="G93" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="H93" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="I93" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="J93" t="n">
+        <v>10</v>
+      </c>
+      <c r="K93" t="n">
         <v>3</v>
       </c>
     </row>
@@ -3890,18 +4172,21 @@
         <v>38</v>
       </c>
       <c r="F94" t="n">
-        <v>21</v>
+        <v>7</v>
       </c>
       <c r="G94" t="n">
-        <v>20</v>
+        <v>8</v>
       </c>
       <c r="H94" t="n">
-        <v>21</v>
+        <v>10</v>
       </c>
       <c r="I94" t="n">
-        <v>10</v>
+        <v>16</v>
       </c>
       <c r="J94" t="n">
+        <v>31</v>
+      </c>
+      <c r="K94" t="n">
         <v>7</v>
       </c>
     </row>
@@ -3926,18 +4211,21 @@
         <v>39</v>
       </c>
       <c r="F95" t="n">
+        <v>4</v>
+      </c>
+      <c r="G95" t="n">
+        <v>13</v>
+      </c>
+      <c r="H95" t="n">
+        <v>5</v>
+      </c>
+      <c r="I95" t="n">
         <v>19</v>
       </c>
-      <c r="G95" t="n">
-        <v>22</v>
-      </c>
-      <c r="H95" t="n">
-        <v>18</v>
-      </c>
-      <c r="I95" t="n">
-        <v>15</v>
-      </c>
       <c r="J95" t="n">
+        <v>33</v>
+      </c>
+      <c r="K95" t="n">
         <v>9</v>
       </c>
     </row>
@@ -3962,18 +4250,21 @@
         <v>59</v>
       </c>
       <c r="F96" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="G96" t="n">
-        <v>27</v>
+        <v>7</v>
       </c>
       <c r="H96" t="n">
-        <v>26</v>
+        <v>8</v>
       </c>
       <c r="I96" t="n">
-        <v>43</v>
+        <v>22</v>
       </c>
       <c r="J96" t="n">
+        <v>69</v>
+      </c>
+      <c r="K96" t="n">
         <v>8</v>
       </c>
     </row>
@@ -3998,18 +4289,21 @@
         <v>23</v>
       </c>
       <c r="F97" t="n">
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="G97" t="n">
-        <v>9</v>
+        <v>4</v>
       </c>
       <c r="H97" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="I97" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="J97" t="n">
+        <v>17</v>
+      </c>
+      <c r="K97" t="n">
         <v>3</v>
       </c>
     </row>
@@ -4034,18 +4328,21 @@
         <v>45</v>
       </c>
       <c r="F98" t="n">
-        <v>23</v>
+        <v>5</v>
       </c>
       <c r="G98" t="n">
+        <v>10</v>
+      </c>
+      <c r="H98" t="n">
         <v>15</v>
       </c>
-      <c r="H98" t="n">
-        <v>22</v>
-      </c>
       <c r="I98" t="n">
-        <v>15</v>
+        <v>8</v>
       </c>
       <c r="J98" t="n">
+        <v>37</v>
+      </c>
+      <c r="K98" t="n">
         <v>12</v>
       </c>
     </row>
@@ -4070,18 +4367,21 @@
         <v>56</v>
       </c>
       <c r="F99" t="n">
-        <v>25</v>
+        <v>6</v>
       </c>
       <c r="G99" t="n">
-        <v>35</v>
+        <v>12</v>
       </c>
       <c r="H99" t="n">
-        <v>22</v>
+        <v>15</v>
       </c>
       <c r="I99" t="n">
-        <v>22</v>
+        <v>27</v>
       </c>
       <c r="J99" t="n">
+        <v>44</v>
+      </c>
+      <c r="K99" t="n">
         <v>4</v>
       </c>
     </row>
@@ -4106,18 +4406,21 @@
         <v>63</v>
       </c>
       <c r="F100" t="n">
-        <v>22</v>
+        <v>6</v>
       </c>
       <c r="G100" t="n">
-        <v>33</v>
+        <v>12</v>
       </c>
       <c r="H100" t="n">
-        <v>24</v>
+        <v>7</v>
       </c>
       <c r="I100" t="n">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="J100" t="n">
+        <v>56</v>
+      </c>
+      <c r="K100" t="n">
         <v>11</v>
       </c>
     </row>
@@ -4142,18 +4445,21 @@
         <v>22</v>
       </c>
       <c r="F101" t="n">
-        <v>7</v>
+        <v>2</v>
       </c>
       <c r="G101" t="n">
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="H101" t="n">
-        <v>13</v>
+        <v>4</v>
       </c>
       <c r="I101" t="n">
         <v>7</v>
       </c>
       <c r="J101" t="n">
+        <v>20</v>
+      </c>
+      <c r="K101" t="n">
         <v>8</v>
       </c>
     </row>
@@ -4178,18 +4484,21 @@
         <v>36</v>
       </c>
       <c r="F102" t="n">
-        <v>11</v>
+        <v>2</v>
       </c>
       <c r="G102" t="n">
-        <v>17</v>
+        <v>5</v>
       </c>
       <c r="H102" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="I102" t="n">
-        <v>21</v>
+        <v>14</v>
       </c>
       <c r="J102" t="n">
+        <v>29</v>
+      </c>
+      <c r="K102" t="n">
         <v>9</v>
       </c>
     </row>
@@ -4214,18 +4523,21 @@
         <v>46</v>
       </c>
       <c r="F103" t="n">
-        <v>13</v>
+        <v>6</v>
       </c>
       <c r="G103" t="n">
-        <v>14</v>
+        <v>3</v>
       </c>
       <c r="H103" t="n">
-        <v>29</v>
+        <v>9</v>
       </c>
       <c r="I103" t="n">
-        <v>16</v>
+        <v>9</v>
       </c>
       <c r="J103" t="n">
+        <v>45</v>
+      </c>
+      <c r="K103" t="n">
         <v>13</v>
       </c>
     </row>
@@ -4250,18 +4562,21 @@
         <v>34</v>
       </c>
       <c r="F104" t="n">
-        <v>10</v>
+        <v>2</v>
       </c>
       <c r="G104" t="n">
-        <v>20</v>
+        <v>6</v>
       </c>
       <c r="H104" t="n">
-        <v>19</v>
+        <v>8</v>
       </c>
       <c r="I104" t="n">
         <v>14</v>
       </c>
       <c r="J104" t="n">
+        <v>33</v>
+      </c>
+      <c r="K104" t="n">
         <v>9</v>
       </c>
     </row>
@@ -4286,18 +4601,21 @@
         <v>23</v>
       </c>
       <c r="F105" t="n">
-        <v>13</v>
+        <v>6</v>
       </c>
       <c r="G105" t="n">
-        <v>14</v>
+        <v>5</v>
       </c>
       <c r="H105" t="n">
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="I105" t="n">
-        <v>8</v>
+        <v>12</v>
       </c>
       <c r="J105" t="n">
+        <v>18</v>
+      </c>
+      <c r="K105" t="n">
         <v>0</v>
       </c>
     </row>
@@ -4322,18 +4640,21 @@
         <v>13</v>
       </c>
       <c r="F106" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="G106" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="H106" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="I106" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="J106" t="n">
+        <v>15</v>
+      </c>
+      <c r="K106" t="n">
         <v>3</v>
       </c>
     </row>
@@ -4358,18 +4679,21 @@
         <v>21</v>
       </c>
       <c r="F107" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="G107" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="H107" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="I107" t="n">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="J107" t="n">
+        <v>14</v>
+      </c>
+      <c r="K107" t="n">
         <v>15</v>
       </c>
     </row>
@@ -4394,18 +4718,21 @@
         <v>58</v>
       </c>
       <c r="F108" t="n">
-        <v>18</v>
+        <v>8</v>
       </c>
       <c r="G108" t="n">
-        <v>39</v>
+        <v>7</v>
       </c>
       <c r="H108" t="n">
-        <v>16</v>
+        <v>6</v>
       </c>
       <c r="I108" t="n">
-        <v>14</v>
+        <v>36</v>
       </c>
       <c r="J108" t="n">
+        <v>30</v>
+      </c>
+      <c r="K108" t="n">
         <v>16</v>
       </c>
     </row>
@@ -4430,18 +4757,21 @@
         <v>54</v>
       </c>
       <c r="F109" t="n">
-        <v>24</v>
+        <v>7</v>
       </c>
       <c r="G109" t="n">
-        <v>21</v>
+        <v>12</v>
       </c>
       <c r="H109" t="n">
-        <v>21</v>
+        <v>8</v>
       </c>
       <c r="I109" t="n">
-        <v>23</v>
+        <v>18</v>
       </c>
       <c r="J109" t="n">
+        <v>44</v>
+      </c>
+      <c r="K109" t="n">
         <v>17</v>
       </c>
     </row>
@@ -4466,18 +4796,21 @@
         <v>58</v>
       </c>
       <c r="F110" t="n">
+        <v>8</v>
+      </c>
+      <c r="G110" t="n">
+        <v>10</v>
+      </c>
+      <c r="H110" t="n">
+        <v>11</v>
+      </c>
+      <c r="I110" t="n">
         <v>21</v>
       </c>
-      <c r="G110" t="n">
-        <v>29</v>
-      </c>
-      <c r="H110" t="n">
-        <v>27</v>
-      </c>
-      <c r="I110" t="n">
-        <v>23</v>
-      </c>
       <c r="J110" t="n">
+        <v>50</v>
+      </c>
+      <c r="K110" t="n">
         <v>4</v>
       </c>
     </row>
@@ -4502,18 +4835,21 @@
         <v>72</v>
       </c>
       <c r="F111" t="n">
-        <v>30</v>
+        <v>4</v>
       </c>
       <c r="G111" t="n">
-        <v>35</v>
+        <v>11</v>
       </c>
       <c r="H111" t="n">
+        <v>22</v>
+      </c>
+      <c r="I111" t="n">
         <v>28</v>
       </c>
-      <c r="I111" t="n">
-        <v>25</v>
-      </c>
       <c r="J111" t="n">
+        <v>53</v>
+      </c>
+      <c r="K111" t="n">
         <v>12</v>
       </c>
     </row>
@@ -4538,18 +4874,21 @@
         <v>21</v>
       </c>
       <c r="F112" t="n">
-        <v>7</v>
+        <v>2</v>
       </c>
       <c r="G112" t="n">
-        <v>11</v>
+        <v>4</v>
       </c>
       <c r="H112" t="n">
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="I112" t="n">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="J112" t="n">
+        <v>22</v>
+      </c>
+      <c r="K112" t="n">
         <v>4</v>
       </c>
     </row>
@@ -4574,18 +4913,21 @@
         <v>15</v>
       </c>
       <c r="F113" t="n">
-        <v>9</v>
+        <v>2</v>
       </c>
       <c r="G113" t="n">
+        <v>7</v>
+      </c>
+      <c r="H113" t="n">
+        <v>0</v>
+      </c>
+      <c r="I113" t="n">
         <v>2</v>
       </c>
-      <c r="H113" t="n">
-        <v>5</v>
-      </c>
-      <c r="I113" t="n">
-        <v>6</v>
-      </c>
       <c r="J113" t="n">
+        <v>11</v>
+      </c>
+      <c r="K113" t="n">
         <v>3</v>
       </c>
     </row>
@@ -4610,18 +4952,21 @@
         <v>49</v>
       </c>
       <c r="F114" t="n">
-        <v>18</v>
+        <v>5</v>
       </c>
       <c r="G114" t="n">
-        <v>21</v>
+        <v>13</v>
       </c>
       <c r="H114" t="n">
-        <v>15</v>
+        <v>7</v>
       </c>
       <c r="I114" t="n">
-        <v>22</v>
+        <v>14</v>
       </c>
       <c r="J114" t="n">
+        <v>37</v>
+      </c>
+      <c r="K114" t="n">
         <v>13</v>
       </c>
     </row>
@@ -4646,18 +4991,21 @@
         <v>39</v>
       </c>
       <c r="F115" t="n">
-        <v>23</v>
+        <v>7</v>
       </c>
       <c r="G115" t="n">
-        <v>18</v>
+        <v>11</v>
       </c>
       <c r="H115" t="n">
-        <v>21</v>
+        <v>7</v>
       </c>
       <c r="I115" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="J115" t="n">
+        <v>36</v>
+      </c>
+      <c r="K115" t="n">
         <v>6</v>
       </c>
     </row>
@@ -4682,18 +5030,21 @@
         <v>34</v>
       </c>
       <c r="F116" t="n">
-        <v>9</v>
+        <v>4</v>
       </c>
       <c r="G116" t="n">
+        <v>2</v>
+      </c>
+      <c r="H116" t="n">
+        <v>3</v>
+      </c>
+      <c r="I116" t="n">
         <v>7</v>
       </c>
-      <c r="H116" t="n">
-        <v>7</v>
-      </c>
-      <c r="I116" t="n">
-        <v>20</v>
-      </c>
       <c r="J116" t="n">
+        <v>27</v>
+      </c>
+      <c r="K116" t="n">
         <v>7</v>
       </c>
     </row>
@@ -4718,18 +5069,21 @@
         <v>36</v>
       </c>
       <c r="F117" t="n">
-        <v>16</v>
+        <v>3</v>
       </c>
       <c r="G117" t="n">
-        <v>19</v>
+        <v>10</v>
       </c>
       <c r="H117" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="I117" t="n">
-        <v>18</v>
+        <v>14</v>
       </c>
       <c r="J117" t="n">
+        <v>28</v>
+      </c>
+      <c r="K117" t="n">
         <v>7</v>
       </c>
     </row>
@@ -4754,18 +5108,21 @@
         <v>58</v>
       </c>
       <c r="F118" t="n">
-        <v>20</v>
+        <v>4</v>
       </c>
       <c r="G118" t="n">
-        <v>29</v>
+        <v>13</v>
       </c>
       <c r="H118" t="n">
+        <v>9</v>
+      </c>
+      <c r="I118" t="n">
         <v>23</v>
       </c>
-      <c r="I118" t="n">
-        <v>22</v>
-      </c>
       <c r="J118" t="n">
+        <v>45</v>
+      </c>
+      <c r="K118" t="n">
         <v>16</v>
       </c>
     </row>
@@ -4790,18 +5147,21 @@
         <v>54</v>
       </c>
       <c r="F119" t="n">
-        <v>14</v>
+        <v>3</v>
       </c>
       <c r="G119" t="n">
-        <v>20</v>
+        <v>8</v>
       </c>
       <c r="H119" t="n">
-        <v>18</v>
+        <v>10</v>
       </c>
       <c r="I119" t="n">
-        <v>25</v>
+        <v>13</v>
       </c>
       <c r="J119" t="n">
+        <v>43</v>
+      </c>
+      <c r="K119" t="n">
         <v>18</v>
       </c>
     </row>
@@ -4826,18 +5186,21 @@
         <v>59</v>
       </c>
       <c r="F120" t="n">
-        <v>18</v>
+        <v>9</v>
       </c>
       <c r="G120" t="n">
-        <v>33</v>
+        <v>8</v>
       </c>
       <c r="H120" t="n">
+        <v>6</v>
+      </c>
+      <c r="I120" t="n">
         <v>28</v>
       </c>
-      <c r="I120" t="n">
-        <v>24</v>
-      </c>
       <c r="J120" t="n">
+        <v>52</v>
+      </c>
+      <c r="K120" t="n">
         <v>11</v>
       </c>
     </row>
@@ -4862,18 +5225,21 @@
         <v>30</v>
       </c>
       <c r="F121" t="n">
-        <v>15</v>
+        <v>5</v>
       </c>
       <c r="G121" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="H121" t="n">
-        <v>17</v>
+        <v>3</v>
       </c>
       <c r="I121" t="n">
         <v>8</v>
       </c>
       <c r="J121" t="n">
+        <v>25</v>
+      </c>
+      <c r="K121" t="n">
         <v>3</v>
       </c>
     </row>
@@ -4898,18 +5264,21 @@
         <v>44</v>
       </c>
       <c r="F122" t="n">
-        <v>25</v>
+        <v>9</v>
       </c>
       <c r="G122" t="n">
-        <v>20</v>
+        <v>12</v>
       </c>
       <c r="H122" t="n">
-        <v>20</v>
+        <v>11</v>
       </c>
       <c r="I122" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="J122" t="n">
+        <v>32</v>
+      </c>
+      <c r="K122" t="n">
         <v>3</v>
       </c>
     </row>
@@ -4934,18 +5303,21 @@
         <v>52</v>
       </c>
       <c r="F123" t="n">
-        <v>15</v>
+        <v>6</v>
       </c>
       <c r="G123" t="n">
-        <v>25</v>
+        <v>7</v>
       </c>
       <c r="H123" t="n">
-        <v>19</v>
+        <v>6</v>
       </c>
       <c r="I123" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="J123" t="n">
+        <v>41</v>
+      </c>
+      <c r="K123" t="n">
         <v>7</v>
       </c>
     </row>
@@ -4970,18 +5342,21 @@
         <v>3</v>
       </c>
       <c r="F124" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="G124" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="H124" t="n">
         <v>2</v>
       </c>
       <c r="I124" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="J124" t="n">
+        <v>3</v>
+      </c>
+      <c r="K124" t="n">
         <v>0</v>
       </c>
     </row>
@@ -5006,18 +5381,21 @@
         <v>46</v>
       </c>
       <c r="F125" t="n">
-        <v>18</v>
+        <v>4</v>
       </c>
       <c r="G125" t="n">
-        <v>13</v>
+        <v>9</v>
       </c>
       <c r="H125" t="n">
-        <v>26</v>
+        <v>11</v>
       </c>
       <c r="I125" t="n">
-        <v>17</v>
+        <v>7</v>
       </c>
       <c r="J125" t="n">
+        <v>43</v>
+      </c>
+      <c r="K125" t="n">
         <v>8</v>
       </c>
     </row>
@@ -5042,18 +5420,21 @@
         <v>46</v>
       </c>
       <c r="F126" t="n">
-        <v>16</v>
+        <v>5</v>
       </c>
       <c r="G126" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="H126" t="n">
-        <v>18</v>
+        <v>5</v>
       </c>
       <c r="I126" t="n">
-        <v>19</v>
+        <v>7</v>
       </c>
       <c r="J126" t="n">
+        <v>37</v>
+      </c>
+      <c r="K126" t="n">
         <v>13</v>
       </c>
     </row>
@@ -5078,18 +5459,21 @@
         <v>22</v>
       </c>
       <c r="F127" t="n">
+        <v>2</v>
+      </c>
+      <c r="G127" t="n">
+        <v>2</v>
+      </c>
+      <c r="H127" t="n">
         <v>7</v>
       </c>
-      <c r="G127" t="n">
-        <v>7</v>
-      </c>
-      <c r="H127" t="n">
-        <v>12</v>
-      </c>
       <c r="I127" t="n">
-        <v>12</v>
+        <v>3</v>
       </c>
       <c r="J127" t="n">
+        <v>24</v>
+      </c>
+      <c r="K127" t="n">
         <v>9</v>
       </c>
     </row>
@@ -5114,18 +5498,21 @@
         <v>8</v>
       </c>
       <c r="F128" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="G128" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="H128" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="I128" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="J128" t="n">
+        <v>8</v>
+      </c>
+      <c r="K128" t="n">
         <v>0</v>
       </c>
     </row>
@@ -5150,18 +5537,21 @@
         <v>14</v>
       </c>
       <c r="F129" t="n">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="G129" t="n">
         <v>4</v>
       </c>
       <c r="H129" t="n">
-        <v>8</v>
+        <v>3</v>
       </c>
       <c r="I129" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="J129" t="n">
+        <v>13</v>
+      </c>
+      <c r="K129" t="n">
         <v>3</v>
       </c>
     </row>
@@ -5186,18 +5576,21 @@
         <v>37</v>
       </c>
       <c r="F130" t="n">
-        <v>14</v>
+        <v>1</v>
       </c>
       <c r="G130" t="n">
-        <v>22</v>
+        <v>9</v>
       </c>
       <c r="H130" t="n">
+        <v>11</v>
+      </c>
+      <c r="I130" t="n">
         <v>15</v>
       </c>
-      <c r="I130" t="n">
-        <v>18</v>
-      </c>
       <c r="J130" t="n">
+        <v>33</v>
+      </c>
+      <c r="K130" t="n">
         <v>11</v>
       </c>
     </row>
@@ -5222,18 +5615,21 @@
         <v>29</v>
       </c>
       <c r="F131" t="n">
-        <v>11</v>
+        <v>4</v>
       </c>
       <c r="G131" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="H131" t="n">
-        <v>21</v>
+        <v>1</v>
       </c>
       <c r="I131" t="n">
-        <v>11</v>
+        <v>5</v>
       </c>
       <c r="J131" t="n">
+        <v>32</v>
+      </c>
+      <c r="K131" t="n">
         <v>10</v>
       </c>
     </row>
@@ -5258,18 +5654,21 @@
         <v>28</v>
       </c>
       <c r="F132" t="n">
-        <v>11</v>
+        <v>1</v>
       </c>
       <c r="G132" t="n">
-        <v>16</v>
+        <v>7</v>
       </c>
       <c r="H132" t="n">
-        <v>12</v>
+        <v>5</v>
       </c>
       <c r="I132" t="n">
-        <v>6</v>
+        <v>14</v>
       </c>
       <c r="J132" t="n">
+        <v>18</v>
+      </c>
+      <c r="K132" t="n">
         <v>3</v>
       </c>
     </row>
@@ -5294,18 +5693,21 @@
         <v>33</v>
       </c>
       <c r="F133" t="n">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="G133" t="n">
-        <v>15</v>
+        <v>3</v>
       </c>
       <c r="H133" t="n">
-        <v>16</v>
+        <v>2</v>
       </c>
       <c r="I133" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="J133" t="n">
+        <v>29</v>
+      </c>
+      <c r="K133" t="n">
         <v>8</v>
       </c>
     </row>
@@ -5330,18 +5732,21 @@
         <v>16</v>
       </c>
       <c r="F134" t="n">
+        <v>1</v>
+      </c>
+      <c r="G134" t="n">
+        <v>4</v>
+      </c>
+      <c r="H134" t="n">
+        <v>5</v>
+      </c>
+      <c r="I134" t="n">
         <v>7</v>
       </c>
-      <c r="G134" t="n">
-        <v>10</v>
-      </c>
-      <c r="H134" t="n">
-        <v>7</v>
-      </c>
-      <c r="I134" t="n">
-        <v>5</v>
-      </c>
       <c r="J134" t="n">
+        <v>12</v>
+      </c>
+      <c r="K134" t="n">
         <v>4</v>
       </c>
     </row>
@@ -5366,18 +5771,21 @@
         <v>34</v>
       </c>
       <c r="F135" t="n">
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="G135" t="n">
-        <v>19</v>
+        <v>4</v>
       </c>
       <c r="H135" t="n">
-        <v>14</v>
+        <v>4</v>
       </c>
       <c r="I135" t="n">
-        <v>13</v>
+        <v>17</v>
       </c>
       <c r="J135" t="n">
+        <v>27</v>
+      </c>
+      <c r="K135" t="n">
         <v>6</v>
       </c>
     </row>
@@ -5402,18 +5810,21 @@
         <v>29</v>
       </c>
       <c r="F136" t="n">
-        <v>11</v>
+        <v>3</v>
       </c>
       <c r="G136" t="n">
-        <v>18</v>
+        <v>5</v>
       </c>
       <c r="H136" t="n">
         <v>6</v>
       </c>
       <c r="I136" t="n">
-        <v>8</v>
+        <v>15</v>
       </c>
       <c r="J136" t="n">
+        <v>14</v>
+      </c>
+      <c r="K136" t="n">
         <v>4</v>
       </c>
     </row>
@@ -5438,18 +5849,21 @@
         <v>42</v>
       </c>
       <c r="F137" t="n">
-        <v>19</v>
+        <v>7</v>
       </c>
       <c r="G137" t="n">
-        <v>25</v>
+        <v>6</v>
       </c>
       <c r="H137" t="n">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="I137" t="n">
-        <v>6</v>
+        <v>18</v>
       </c>
       <c r="J137" t="n">
+        <v>21</v>
+      </c>
+      <c r="K137" t="n">
         <v>1</v>
       </c>
     </row>
@@ -5474,18 +5888,21 @@
         <v>41</v>
       </c>
       <c r="F138" t="n">
-        <v>19</v>
+        <v>7</v>
       </c>
       <c r="G138" t="n">
-        <v>24</v>
+        <v>10</v>
       </c>
       <c r="H138" t="n">
+        <v>8</v>
+      </c>
+      <c r="I138" t="n">
         <v>18</v>
       </c>
-      <c r="I138" t="n">
-        <v>15</v>
-      </c>
       <c r="J138" t="n">
+        <v>33</v>
+      </c>
+      <c r="K138" t="n">
         <v>4</v>
       </c>
     </row>
@@ -5510,18 +5927,21 @@
         <v>21</v>
       </c>
       <c r="F139" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="G139" t="n">
+        <v>2</v>
+      </c>
+      <c r="H139" t="n">
+        <v>0</v>
+      </c>
+      <c r="I139" t="n">
         <v>11</v>
       </c>
-      <c r="H139" t="n">
-        <v>8</v>
-      </c>
-      <c r="I139" t="n">
-        <v>12</v>
-      </c>
       <c r="J139" t="n">
+        <v>20</v>
+      </c>
+      <c r="K139" t="n">
         <v>3</v>
       </c>
     </row>
@@ -5546,18 +5966,21 @@
         <v>12</v>
       </c>
       <c r="F140" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="G140" t="n">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="H140" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="I140" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="J140" t="n">
+        <v>9</v>
+      </c>
+      <c r="K140" t="n">
         <v>1</v>
       </c>
     </row>
@@ -5582,18 +6005,21 @@
         <v>33</v>
       </c>
       <c r="F141" t="n">
-        <v>12</v>
+        <v>2</v>
       </c>
       <c r="G141" t="n">
+        <v>5</v>
+      </c>
+      <c r="H141" t="n">
         <v>9</v>
       </c>
-      <c r="H141" t="n">
-        <v>13</v>
-      </c>
       <c r="I141" t="n">
-        <v>12</v>
+        <v>5</v>
       </c>
       <c r="J141" t="n">
+        <v>25</v>
+      </c>
+      <c r="K141" t="n">
         <v>15</v>
       </c>
     </row>
@@ -5618,18 +6044,21 @@
         <v>34</v>
       </c>
       <c r="F142" t="n">
-        <v>12</v>
+        <v>2</v>
       </c>
       <c r="G142" t="n">
-        <v>19</v>
+        <v>7</v>
       </c>
       <c r="H142" t="n">
-        <v>13</v>
+        <v>8</v>
       </c>
       <c r="I142" t="n">
-        <v>22</v>
+        <v>14</v>
       </c>
       <c r="J142" t="n">
+        <v>35</v>
+      </c>
+      <c r="K142" t="n">
         <v>4</v>
       </c>
     </row>
@@ -5654,18 +6083,21 @@
         <v>26</v>
       </c>
       <c r="F143" t="n">
-        <v>7</v>
+        <v>1</v>
       </c>
       <c r="G143" t="n">
-        <v>13</v>
+        <v>6</v>
       </c>
       <c r="H143" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="I143" t="n">
         <v>11</v>
       </c>
       <c r="J143" t="n">
+        <v>16</v>
+      </c>
+      <c r="K143" t="n">
         <v>6</v>
       </c>
     </row>
@@ -5690,18 +6122,21 @@
         <v>56</v>
       </c>
       <c r="F144" t="n">
-        <v>18</v>
+        <v>5</v>
       </c>
       <c r="G144" t="n">
-        <v>18</v>
+        <v>8</v>
       </c>
       <c r="H144" t="n">
-        <v>20</v>
+        <v>13</v>
       </c>
       <c r="I144" t="n">
-        <v>14</v>
+        <v>10</v>
       </c>
       <c r="J144" t="n">
+        <v>34</v>
+      </c>
+      <c r="K144" t="n">
         <v>18</v>
       </c>
     </row>
@@ -5726,18 +6161,21 @@
         <v>26</v>
       </c>
       <c r="F145" t="n">
-        <v>14</v>
+        <v>8</v>
       </c>
       <c r="G145" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="H145" t="n">
-        <v>16</v>
+        <v>1</v>
       </c>
       <c r="I145" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="J145" t="n">
+        <v>19</v>
+      </c>
+      <c r="K145" t="n">
         <v>10</v>
       </c>
     </row>
@@ -5762,18 +6200,21 @@
         <v>42</v>
       </c>
       <c r="F146" t="n">
-        <v>13</v>
+        <v>5</v>
       </c>
       <c r="G146" t="n">
-        <v>16</v>
+        <v>5</v>
       </c>
       <c r="H146" t="n">
-        <v>18</v>
+        <v>7</v>
       </c>
       <c r="I146" t="n">
-        <v>25</v>
+        <v>12</v>
       </c>
       <c r="J146" t="n">
+        <v>43</v>
+      </c>
+      <c r="K146" t="n">
         <v>11</v>
       </c>
     </row>
@@ -5798,18 +6239,21 @@
         <v>50</v>
       </c>
       <c r="F147" t="n">
-        <v>15</v>
+        <v>4</v>
       </c>
       <c r="G147" t="n">
-        <v>28</v>
+        <v>8</v>
       </c>
       <c r="H147" t="n">
-        <v>24</v>
+        <v>6</v>
       </c>
       <c r="I147" t="n">
-        <v>19</v>
+        <v>25</v>
       </c>
       <c r="J147" t="n">
+        <v>43</v>
+      </c>
+      <c r="K147" t="n">
         <v>10</v>
       </c>
     </row>
@@ -5834,18 +6278,21 @@
         <v>16</v>
       </c>
       <c r="F148" t="n">
-        <v>11</v>
+        <v>3</v>
       </c>
       <c r="G148" t="n">
-        <v>12</v>
+        <v>6</v>
       </c>
       <c r="H148" t="n">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="I148" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="J148" t="n">
+        <v>13</v>
+      </c>
+      <c r="K148" t="n">
         <v>2</v>
       </c>
     </row>
@@ -5870,7 +6317,7 @@
         <v>4</v>
       </c>
       <c r="F149" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="G149" t="n">
         <v>2</v>
@@ -5879,9 +6326,12 @@
         <v>0</v>
       </c>
       <c r="I149" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="J149" t="n">
+        <v>4</v>
+      </c>
+      <c r="K149" t="n">
         <v>1</v>
       </c>
     </row>
@@ -5906,18 +6356,21 @@
         <v>17</v>
       </c>
       <c r="F150" t="n">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="G150" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="H150" t="n">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="I150" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="J150" t="n">
+        <v>13</v>
+      </c>
+      <c r="K150" t="n">
         <v>1</v>
       </c>
     </row>
@@ -5942,18 +6395,21 @@
         <v>57</v>
       </c>
       <c r="F151" t="n">
-        <v>31</v>
+        <v>9</v>
       </c>
       <c r="G151" t="n">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="H151" t="n">
-        <v>38</v>
+        <v>11</v>
       </c>
       <c r="I151" t="n">
-        <v>17</v>
+        <v>7</v>
       </c>
       <c r="J151" t="n">
+        <v>55</v>
+      </c>
+      <c r="K151" t="n">
         <v>8</v>
       </c>
     </row>
@@ -5978,18 +6434,21 @@
         <v>42</v>
       </c>
       <c r="F152" t="n">
-        <v>24</v>
+        <v>7</v>
       </c>
       <c r="G152" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="H152" t="n">
-        <v>18</v>
+        <v>9</v>
       </c>
       <c r="I152" t="n">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="J152" t="n">
+        <v>29</v>
+      </c>
+      <c r="K152" t="n">
         <v>1</v>
       </c>
     </row>
@@ -6014,18 +6473,21 @@
         <v>19</v>
       </c>
       <c r="F153" t="n">
+        <v>2</v>
+      </c>
+      <c r="G153" t="n">
+        <v>3</v>
+      </c>
+      <c r="H153" t="n">
         <v>7</v>
       </c>
-      <c r="G153" t="n">
-        <v>17</v>
-      </c>
-      <c r="H153" t="n">
-        <v>13</v>
-      </c>
       <c r="I153" t="n">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="J153" t="n">
+        <v>23</v>
+      </c>
+      <c r="K153" t="n">
         <v>3</v>
       </c>
     </row>
@@ -6050,18 +6512,21 @@
         <v>54</v>
       </c>
       <c r="F154" t="n">
-        <v>14</v>
+        <v>5</v>
       </c>
       <c r="G154" t="n">
-        <v>22</v>
+        <v>6</v>
       </c>
       <c r="H154" t="n">
+        <v>6</v>
+      </c>
+      <c r="I154" t="n">
         <v>19</v>
       </c>
-      <c r="I154" t="n">
-        <v>34</v>
-      </c>
       <c r="J154" t="n">
+        <v>53</v>
+      </c>
+      <c r="K154" t="n">
         <v>10</v>
       </c>
     </row>
@@ -6086,18 +6551,21 @@
         <v>36</v>
       </c>
       <c r="F155" t="n">
-        <v>13</v>
+        <v>5</v>
       </c>
       <c r="G155" t="n">
-        <v>19</v>
+        <v>5</v>
       </c>
       <c r="H155" t="n">
-        <v>12</v>
+        <v>7</v>
       </c>
       <c r="I155" t="n">
-        <v>18</v>
+        <v>15</v>
       </c>
       <c r="J155" t="n">
+        <v>30</v>
+      </c>
+      <c r="K155" t="n">
         <v>8</v>
       </c>
     </row>
@@ -6122,18 +6590,21 @@
         <v>59</v>
       </c>
       <c r="F156" t="n">
-        <v>23</v>
+        <v>6</v>
       </c>
       <c r="G156" t="n">
-        <v>29</v>
+        <v>11</v>
       </c>
       <c r="H156" t="n">
-        <v>28</v>
+        <v>11</v>
       </c>
       <c r="I156" t="n">
         <v>24</v>
       </c>
       <c r="J156" t="n">
+        <v>52</v>
+      </c>
+      <c r="K156" t="n">
         <v>12</v>
       </c>
     </row>
@@ -6158,18 +6629,21 @@
         <v>47</v>
       </c>
       <c r="F157" t="n">
-        <v>10</v>
+        <v>3</v>
       </c>
       <c r="G157" t="n">
-        <v>22</v>
+        <v>5</v>
       </c>
       <c r="H157" t="n">
-        <v>16</v>
+        <v>3</v>
       </c>
       <c r="I157" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="J157" t="n">
+        <v>36</v>
+      </c>
+      <c r="K157" t="n">
         <v>16</v>
       </c>
     </row>
@@ -6194,18 +6668,21 @@
         <v>23</v>
       </c>
       <c r="F158" t="n">
-        <v>11</v>
+        <v>3</v>
       </c>
       <c r="G158" t="n">
+        <v>5</v>
+      </c>
+      <c r="H158" t="n">
+        <v>3</v>
+      </c>
+      <c r="I158" t="n">
         <v>15</v>
       </c>
-      <c r="H158" t="n">
-        <v>10</v>
-      </c>
-      <c r="I158" t="n">
-        <v>11</v>
-      </c>
       <c r="J158" t="n">
+        <v>21</v>
+      </c>
+      <c r="K158" t="n">
         <v>2</v>
       </c>
     </row>
@@ -6230,18 +6707,21 @@
         <v>9</v>
       </c>
       <c r="F159" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="G159" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="H159" t="n">
-        <v>7</v>
+        <v>2</v>
       </c>
       <c r="I159" t="n">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="J159" t="n">
+        <v>13</v>
+      </c>
+      <c r="K159" t="n">
         <v>3</v>
       </c>
     </row>
@@ -6266,18 +6746,21 @@
         <v>68</v>
       </c>
       <c r="F160" t="n">
-        <v>39</v>
+        <v>15</v>
       </c>
       <c r="G160" t="n">
-        <v>43</v>
+        <v>18</v>
       </c>
       <c r="H160" t="n">
-        <v>32</v>
+        <v>15</v>
       </c>
       <c r="I160" t="n">
-        <v>27</v>
+        <v>34</v>
       </c>
       <c r="J160" t="n">
+        <v>59</v>
+      </c>
+      <c r="K160" t="n">
         <v>11</v>
       </c>
     </row>
@@ -6302,18 +6785,21 @@
         <v>25</v>
       </c>
       <c r="F161" t="n">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="G161" t="n">
-        <v>12</v>
+        <v>3</v>
       </c>
       <c r="H161" t="n">
+        <v>3</v>
+      </c>
+      <c r="I161" t="n">
         <v>10</v>
       </c>
-      <c r="I161" t="n">
-        <v>8</v>
-      </c>
       <c r="J161" t="n">
+        <v>18</v>
+      </c>
+      <c r="K161" t="n">
         <v>10</v>
       </c>
     </row>
@@ -6338,18 +6824,21 @@
         <v>23</v>
       </c>
       <c r="F162" t="n">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="G162" t="n">
         <v>5</v>
       </c>
       <c r="H162" t="n">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="I162" t="n">
-        <v>17</v>
+        <v>4</v>
       </c>
       <c r="J162" t="n">
+        <v>23</v>
+      </c>
+      <c r="K162" t="n">
         <v>4</v>
       </c>
     </row>
@@ -6374,18 +6863,21 @@
         <v>47</v>
       </c>
       <c r="F163" t="n">
-        <v>16</v>
+        <v>5</v>
       </c>
       <c r="G163" t="n">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="H163" t="n">
-        <v>23</v>
+        <v>5</v>
       </c>
       <c r="I163" t="n">
-        <v>21</v>
+        <v>8</v>
       </c>
       <c r="J163" t="n">
+        <v>44</v>
+      </c>
+      <c r="K163" t="n">
         <v>11</v>
       </c>
     </row>
@@ -6410,18 +6902,21 @@
         <v>23</v>
       </c>
       <c r="F164" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="G164" t="n">
-        <v>12</v>
+        <v>2</v>
       </c>
       <c r="H164" t="n">
-        <v>11</v>
+        <v>5</v>
       </c>
       <c r="I164" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="J164" t="n">
+        <v>21</v>
+      </c>
+      <c r="K164" t="n">
         <v>6</v>
       </c>
     </row>
@@ -6446,18 +6941,21 @@
         <v>33</v>
       </c>
       <c r="F165" t="n">
-        <v>13</v>
+        <v>7</v>
       </c>
       <c r="G165" t="n">
-        <v>22</v>
+        <v>3</v>
       </c>
       <c r="H165" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="I165" t="n">
-        <v>14</v>
+        <v>17</v>
       </c>
       <c r="J165" t="n">
+        <v>24</v>
+      </c>
+      <c r="K165" t="n">
         <v>6</v>
       </c>
     </row>
@@ -6482,18 +6980,21 @@
         <v>24</v>
       </c>
       <c r="F166" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="G166" t="n">
-        <v>18</v>
+        <v>1</v>
       </c>
       <c r="H166" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="I166" t="n">
-        <v>12</v>
+        <v>17</v>
       </c>
       <c r="J166" t="n">
+        <v>16</v>
+      </c>
+      <c r="K166" t="n">
         <v>7</v>
       </c>
     </row>
@@ -6518,18 +7019,21 @@
         <v>32</v>
       </c>
       <c r="F167" t="n">
-        <v>13</v>
+        <v>4</v>
       </c>
       <c r="G167" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="H167" t="n">
-        <v>11</v>
+        <v>4</v>
       </c>
       <c r="I167" t="n">
-        <v>13</v>
+        <v>7</v>
       </c>
       <c r="J167" t="n">
+        <v>24</v>
+      </c>
+      <c r="K167" t="n">
         <v>13</v>
       </c>
     </row>
@@ -6554,18 +7058,21 @@
         <v>26</v>
       </c>
       <c r="F168" t="n">
-        <v>18</v>
+        <v>5</v>
       </c>
       <c r="G168" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="H168" t="n">
-        <v>14</v>
+        <v>4</v>
       </c>
       <c r="I168" t="n">
         <v>8</v>
       </c>
       <c r="J168" t="n">
+        <v>22</v>
+      </c>
+      <c r="K168" t="n">
         <v>2</v>
       </c>
     </row>
@@ -6590,18 +7097,21 @@
         <v>18</v>
       </c>
       <c r="F169" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="G169" t="n">
-        <v>10</v>
+        <v>3</v>
       </c>
       <c r="H169" t="n">
-        <v>8</v>
+        <v>2</v>
       </c>
       <c r="I169" t="n">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="J169" t="n">
+        <v>15</v>
+      </c>
+      <c r="K169" t="n">
         <v>1</v>
       </c>
     </row>
@@ -6626,18 +7136,21 @@
         <v>43</v>
       </c>
       <c r="F170" t="n">
-        <v>19</v>
+        <v>6</v>
       </c>
       <c r="G170" t="n">
-        <v>24</v>
+        <v>11</v>
       </c>
       <c r="H170" t="n">
-        <v>19</v>
+        <v>8</v>
       </c>
       <c r="I170" t="n">
-        <v>9</v>
+        <v>18</v>
       </c>
       <c r="J170" t="n">
+        <v>28</v>
+      </c>
+      <c r="K170" t="n">
         <v>5</v>
       </c>
     </row>
@@ -6662,18 +7175,21 @@
         <v>19</v>
       </c>
       <c r="F171" t="n">
-        <v>11</v>
+        <v>4</v>
       </c>
       <c r="G171" t="n">
-        <v>9</v>
+        <v>4</v>
       </c>
       <c r="H171" t="n">
-        <v>13</v>
+        <v>5</v>
       </c>
       <c r="I171" t="n">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="J171" t="n">
+        <v>16</v>
+      </c>
+      <c r="K171" t="n">
         <v>1</v>
       </c>
     </row>
@@ -6698,18 +7214,21 @@
         <v>25</v>
       </c>
       <c r="F172" t="n">
-        <v>13</v>
+        <v>3</v>
       </c>
       <c r="G172" t="n">
-        <v>13</v>
+        <v>8</v>
       </c>
       <c r="H172" t="n">
-        <v>12</v>
+        <v>6</v>
       </c>
       <c r="I172" t="n">
-        <v>4</v>
+        <v>9</v>
       </c>
       <c r="J172" t="n">
+        <v>16</v>
+      </c>
+      <c r="K172" t="n">
         <v>2</v>
       </c>
     </row>
@@ -6734,18 +7253,21 @@
         <v>68</v>
       </c>
       <c r="F173" t="n">
-        <v>39</v>
+        <v>8</v>
       </c>
       <c r="G173" t="n">
-        <v>41</v>
+        <v>18</v>
       </c>
       <c r="H173" t="n">
-        <v>30</v>
+        <v>26</v>
       </c>
       <c r="I173" t="n">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="J173" t="n">
+        <v>57</v>
+      </c>
+      <c r="K173" t="n">
         <v>3</v>
       </c>
     </row>
@@ -6770,18 +7292,21 @@
         <v>28</v>
       </c>
       <c r="F174" t="n">
-        <v>16</v>
+        <v>1</v>
       </c>
       <c r="G174" t="n">
         <v>11</v>
       </c>
       <c r="H174" t="n">
-        <v>16</v>
+        <v>7</v>
       </c>
       <c r="I174" t="n">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="J174" t="n">
+        <v>28</v>
+      </c>
+      <c r="K174" t="n">
         <v>1</v>
       </c>
     </row>
@@ -6806,18 +7331,21 @@
         <v>93</v>
       </c>
       <c r="F175" t="n">
-        <v>48</v>
+        <v>13</v>
       </c>
       <c r="G175" t="n">
-        <v>51</v>
+        <v>26</v>
       </c>
       <c r="H175" t="n">
-        <v>43</v>
+        <v>20</v>
       </c>
       <c r="I175" t="n">
-        <v>36</v>
+        <v>40</v>
       </c>
       <c r="J175" t="n">
+        <v>79</v>
+      </c>
+      <c r="K175" t="n">
         <v>9</v>
       </c>
     </row>
@@ -6842,18 +7370,21 @@
         <v>43</v>
       </c>
       <c r="F176" t="n">
-        <v>23</v>
+        <v>7</v>
       </c>
       <c r="G176" t="n">
-        <v>19</v>
+        <v>11</v>
       </c>
       <c r="H176" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="I176" t="n">
         <v>14</v>
       </c>
       <c r="J176" t="n">
+        <v>34</v>
+      </c>
+      <c r="K176" t="n">
         <v>6</v>
       </c>
     </row>
@@ -6878,18 +7409,21 @@
         <v>30</v>
       </c>
       <c r="F177" t="n">
+        <v>2</v>
+      </c>
+      <c r="G177" t="n">
+        <v>11</v>
+      </c>
+      <c r="H177" t="n">
+        <v>3</v>
+      </c>
+      <c r="I177" t="n">
         <v>14</v>
       </c>
-      <c r="G177" t="n">
-        <v>16</v>
-      </c>
-      <c r="H177" t="n">
-        <v>12</v>
-      </c>
-      <c r="I177" t="n">
-        <v>11</v>
-      </c>
       <c r="J177" t="n">
+        <v>23</v>
+      </c>
+      <c r="K177" t="n">
         <v>2</v>
       </c>
     </row>
@@ -6914,18 +7448,21 @@
         <v>40</v>
       </c>
       <c r="F178" t="n">
-        <v>14</v>
+        <v>4</v>
       </c>
       <c r="G178" t="n">
-        <v>26</v>
+        <v>6</v>
       </c>
       <c r="H178" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="I178" t="n">
-        <v>28</v>
+        <v>21</v>
       </c>
       <c r="J178" t="n">
+        <v>38</v>
+      </c>
+      <c r="K178" t="n">
         <v>5</v>
       </c>
     </row>
@@ -6950,18 +7487,21 @@
         <v>75</v>
       </c>
       <c r="F179" t="n">
-        <v>25</v>
+        <v>7</v>
       </c>
       <c r="G179" t="n">
-        <v>37</v>
+        <v>14</v>
       </c>
       <c r="H179" t="n">
-        <v>32</v>
+        <v>10</v>
       </c>
       <c r="I179" t="n">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="J179" t="n">
+        <v>62</v>
+      </c>
+      <c r="K179" t="n">
         <v>8</v>
       </c>
     </row>
@@ -6986,18 +7526,21 @@
         <v>57</v>
       </c>
       <c r="F180" t="n">
-        <v>24</v>
+        <v>10</v>
       </c>
       <c r="G180" t="n">
-        <v>31</v>
+        <v>11</v>
       </c>
       <c r="H180" t="n">
-        <v>24</v>
+        <v>5</v>
       </c>
       <c r="I180" t="n">
-        <v>24</v>
+        <v>29</v>
       </c>
       <c r="J180" t="n">
+        <v>48</v>
+      </c>
+      <c r="K180" t="n">
         <v>8</v>
       </c>
     </row>
@@ -7022,18 +7565,21 @@
         <v>23</v>
       </c>
       <c r="F181" t="n">
-        <v>8</v>
+        <v>1</v>
       </c>
       <c r="G181" t="n">
-        <v>14</v>
+        <v>6</v>
       </c>
       <c r="H181" t="n">
-        <v>12</v>
+        <v>4</v>
       </c>
       <c r="I181" t="n">
         <v>11</v>
       </c>
       <c r="J181" t="n">
+        <v>23</v>
+      </c>
+      <c r="K181" t="n">
         <v>5</v>
       </c>
     </row>
@@ -7058,18 +7604,21 @@
         <v>16</v>
       </c>
       <c r="F182" t="n">
+        <v>2</v>
+      </c>
+      <c r="G182" t="n">
+        <v>5</v>
+      </c>
+      <c r="H182" t="n">
+        <v>2</v>
+      </c>
+      <c r="I182" t="n">
         <v>7</v>
       </c>
-      <c r="G182" t="n">
-        <v>9</v>
-      </c>
-      <c r="H182" t="n">
-        <v>7</v>
-      </c>
-      <c r="I182" t="n">
-        <v>6</v>
-      </c>
       <c r="J182" t="n">
+        <v>13</v>
+      </c>
+      <c r="K182" t="n">
         <v>1</v>
       </c>
     </row>
@@ -7094,18 +7643,21 @@
         <v>144</v>
       </c>
       <c r="F183" t="n">
-        <v>78</v>
+        <v>21</v>
       </c>
       <c r="G183" t="n">
-        <v>56</v>
+        <v>35</v>
       </c>
       <c r="H183" t="n">
-        <v>72</v>
+        <v>38</v>
       </c>
       <c r="I183" t="n">
-        <v>43</v>
+        <v>40</v>
       </c>
       <c r="J183" t="n">
+        <v>115</v>
+      </c>
+      <c r="K183" t="n">
         <v>12</v>
       </c>
     </row>
@@ -7130,18 +7682,21 @@
         <v>29</v>
       </c>
       <c r="F184" t="n">
-        <v>17</v>
+        <v>5</v>
       </c>
       <c r="G184" t="n">
-        <v>18</v>
+        <v>9</v>
       </c>
       <c r="H184" t="n">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="I184" t="n">
-        <v>7</v>
+        <v>14</v>
       </c>
       <c r="J184" t="n">
+        <v>16</v>
+      </c>
+      <c r="K184" t="n">
         <v>2</v>
       </c>
     </row>
@@ -7166,18 +7721,21 @@
         <v>6</v>
       </c>
       <c r="F185" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G185" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="H185" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="I185" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="J185" t="n">
+        <v>6</v>
+      </c>
+      <c r="K185" t="n">
         <v>0</v>
       </c>
     </row>
@@ -7202,18 +7760,21 @@
         <v>10</v>
       </c>
       <c r="F186" t="n">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="G186" t="n">
         <v>3</v>
       </c>
       <c r="H186" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="I186" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="J186" t="n">
+        <v>9</v>
+      </c>
+      <c r="K186" t="n">
         <v>1</v>
       </c>
     </row>
@@ -7238,18 +7799,21 @@
         <v>10</v>
       </c>
       <c r="F187" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="G187" t="n">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="H187" t="n">
+        <v>3</v>
+      </c>
+      <c r="I187" t="n">
+        <v>5</v>
+      </c>
+      <c r="J187" t="n">
         <v>7</v>
       </c>
-      <c r="I187" t="n">
-        <v>0</v>
-      </c>
-      <c r="J187" t="n">
+      <c r="K187" t="n">
         <v>3</v>
       </c>
     </row>
@@ -7274,18 +7838,21 @@
         <v>24</v>
       </c>
       <c r="F188" t="n">
-        <v>15</v>
+        <v>4</v>
       </c>
       <c r="G188" t="n">
+        <v>9</v>
+      </c>
+      <c r="H188" t="n">
+        <v>2</v>
+      </c>
+      <c r="I188" t="n">
         <v>7</v>
       </c>
-      <c r="H188" t="n">
-        <v>20</v>
-      </c>
-      <c r="I188" t="n">
-        <v>6</v>
-      </c>
       <c r="J188" t="n">
+        <v>26</v>
+      </c>
+      <c r="K188" t="n">
         <v>3</v>
       </c>
     </row>
@@ -7310,18 +7877,21 @@
         <v>24</v>
       </c>
       <c r="F189" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="G189" t="n">
+        <v>1</v>
+      </c>
+      <c r="H189" t="n">
+        <v>3</v>
+      </c>
+      <c r="I189" t="n">
+        <v>14</v>
+      </c>
+      <c r="J189" t="n">
         <v>17</v>
       </c>
-      <c r="H189" t="n">
-        <v>5</v>
-      </c>
-      <c r="I189" t="n">
-        <v>12</v>
-      </c>
-      <c r="J189" t="n">
+      <c r="K189" t="n">
         <v>3</v>
       </c>
     </row>
@@ -7346,18 +7916,21 @@
         <v>31</v>
       </c>
       <c r="F190" t="n">
-        <v>11</v>
+        <v>3</v>
       </c>
       <c r="G190" t="n">
-        <v>15</v>
+        <v>4</v>
       </c>
       <c r="H190" t="n">
-        <v>13</v>
+        <v>7</v>
       </c>
       <c r="I190" t="n">
         <v>12</v>
       </c>
       <c r="J190" t="n">
+        <v>25</v>
+      </c>
+      <c r="K190" t="n">
         <v>0</v>
       </c>
     </row>
@@ -7382,18 +7955,21 @@
         <v>8</v>
       </c>
       <c r="F191" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="G191" t="n">
+        <v>0</v>
+      </c>
+      <c r="H191" t="n">
+        <v>3</v>
+      </c>
+      <c r="I191" t="n">
+        <v>8</v>
+      </c>
+      <c r="J191" t="n">
         <v>9</v>
       </c>
-      <c r="H191" t="n">
-        <v>5</v>
-      </c>
-      <c r="I191" t="n">
-        <v>4</v>
-      </c>
-      <c r="J191" t="n">
+      <c r="K191" t="n">
         <v>0</v>
       </c>
     </row>
@@ -7418,18 +7994,21 @@
         <v>53</v>
       </c>
       <c r="F192" t="n">
-        <v>24</v>
+        <v>9</v>
       </c>
       <c r="G192" t="n">
-        <v>27</v>
+        <v>10</v>
       </c>
       <c r="H192" t="n">
-        <v>21</v>
+        <v>7</v>
       </c>
       <c r="I192" t="n">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="J192" t="n">
+        <v>48</v>
+      </c>
+      <c r="K192" t="n">
         <v>11</v>
       </c>
     </row>
@@ -7454,18 +8033,21 @@
         <v>53</v>
       </c>
       <c r="F193" t="n">
-        <v>32</v>
+        <v>9</v>
       </c>
       <c r="G193" t="n">
-        <v>22</v>
+        <v>16</v>
       </c>
       <c r="H193" t="n">
-        <v>29</v>
+        <v>12</v>
       </c>
       <c r="I193" t="n">
-        <v>12</v>
+        <v>17</v>
       </c>
       <c r="J193" t="n">
+        <v>41</v>
+      </c>
+      <c r="K193" t="n">
         <v>5</v>
       </c>
     </row>
@@ -7490,18 +8072,21 @@
         <v>45</v>
       </c>
       <c r="F194" t="n">
+        <v>10</v>
+      </c>
+      <c r="G194" t="n">
+        <v>10</v>
+      </c>
+      <c r="H194" t="n">
+        <v>6</v>
+      </c>
+      <c r="I194" t="n">
         <v>20</v>
       </c>
-      <c r="G194" t="n">
-        <v>26</v>
-      </c>
-      <c r="H194" t="n">
-        <v>18</v>
-      </c>
-      <c r="I194" t="n">
-        <v>11</v>
-      </c>
       <c r="J194" t="n">
+        <v>29</v>
+      </c>
+      <c r="K194" t="n">
         <v>7</v>
       </c>
     </row>
@@ -7526,18 +8111,21 @@
         <v>27</v>
       </c>
       <c r="F195" t="n">
-        <v>14</v>
+        <v>1</v>
       </c>
       <c r="G195" t="n">
         <v>11</v>
       </c>
       <c r="H195" t="n">
-        <v>16</v>
+        <v>5</v>
       </c>
       <c r="I195" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="J195" t="n">
+        <v>23</v>
+      </c>
+      <c r="K195" t="n">
         <v>3</v>
       </c>
     </row>
@@ -7562,18 +8150,21 @@
         <v>38</v>
       </c>
       <c r="F196" t="n">
-        <v>16</v>
+        <v>9</v>
       </c>
       <c r="G196" t="n">
-        <v>17</v>
+        <v>5</v>
       </c>
       <c r="H196" t="n">
-        <v>17</v>
+        <v>8</v>
       </c>
       <c r="I196" t="n">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="J196" t="n">
+        <v>30</v>
+      </c>
+      <c r="K196" t="n">
         <v>8</v>
       </c>
     </row>
@@ -7598,18 +8189,21 @@
         <v>39</v>
       </c>
       <c r="F197" t="n">
-        <v>21</v>
+        <v>3</v>
       </c>
       <c r="G197" t="n">
-        <v>23</v>
+        <v>13</v>
       </c>
       <c r="H197" t="n">
-        <v>24</v>
+        <v>17</v>
       </c>
       <c r="I197" t="n">
-        <v>7</v>
+        <v>11</v>
       </c>
       <c r="J197" t="n">
+        <v>31</v>
+      </c>
+      <c r="K197" t="n">
         <v>3</v>
       </c>
     </row>
@@ -7634,18 +8228,21 @@
         <v>37</v>
       </c>
       <c r="F198" t="n">
-        <v>16</v>
+        <v>5</v>
       </c>
       <c r="G198" t="n">
-        <v>19</v>
+        <v>9</v>
       </c>
       <c r="H198" t="n">
-        <v>18</v>
+        <v>6</v>
       </c>
       <c r="I198" t="n">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="J198" t="n">
+        <v>31</v>
+      </c>
+      <c r="K198" t="n">
         <v>5</v>
       </c>
     </row>
@@ -7670,18 +8267,21 @@
         <v>24</v>
       </c>
       <c r="F199" t="n">
-        <v>9</v>
+        <v>3</v>
       </c>
       <c r="G199" t="n">
-        <v>12</v>
+        <v>3</v>
       </c>
       <c r="H199" t="n">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="I199" t="n">
-        <v>16</v>
+        <v>10</v>
       </c>
       <c r="J199" t="n">
+        <v>25</v>
+      </c>
+      <c r="K199" t="n">
         <v>4</v>
       </c>
     </row>
@@ -7706,18 +8306,21 @@
         <v>58</v>
       </c>
       <c r="F200" t="n">
-        <v>35</v>
+        <v>12</v>
       </c>
       <c r="G200" t="n">
-        <v>30</v>
+        <v>15</v>
       </c>
       <c r="H200" t="n">
-        <v>31</v>
+        <v>16</v>
       </c>
       <c r="I200" t="n">
-        <v>12</v>
+        <v>22</v>
       </c>
       <c r="J200" t="n">
+        <v>43</v>
+      </c>
+      <c r="K200" t="n">
         <v>6</v>
       </c>
     </row>
@@ -7742,18 +8345,21 @@
         <v>71</v>
       </c>
       <c r="F201" t="n">
-        <v>37</v>
+        <v>8</v>
       </c>
       <c r="G201" t="n">
-        <v>36</v>
+        <v>18</v>
       </c>
       <c r="H201" t="n">
-        <v>35</v>
+        <v>20</v>
       </c>
       <c r="I201" t="n">
-        <v>23</v>
+        <v>27</v>
       </c>
       <c r="J201" t="n">
+        <v>58</v>
+      </c>
+      <c r="K201" t="n">
         <v>6</v>
       </c>
     </row>
@@ -7778,18 +8384,21 @@
         <v>66</v>
       </c>
       <c r="F202" t="n">
-        <v>28</v>
+        <v>9</v>
       </c>
       <c r="G202" t="n">
-        <v>29</v>
+        <v>14</v>
       </c>
       <c r="H202" t="n">
-        <v>28</v>
+        <v>11</v>
       </c>
       <c r="I202" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="J202" t="n">
+        <v>50</v>
+      </c>
+      <c r="K202" t="n">
         <v>10</v>
       </c>
     </row>
@@ -7814,18 +8423,21 @@
         <v>24</v>
       </c>
       <c r="F203" t="n">
-        <v>8</v>
+        <v>3</v>
       </c>
       <c r="G203" t="n">
-        <v>17</v>
+        <v>4</v>
       </c>
       <c r="H203" t="n">
-        <v>7</v>
+        <v>2</v>
       </c>
       <c r="I203" t="n">
-        <v>11</v>
+        <v>16</v>
       </c>
       <c r="J203" t="n">
+        <v>18</v>
+      </c>
+      <c r="K203" t="n">
         <v>5</v>
       </c>
     </row>
@@ -7850,18 +8462,21 @@
         <v>13</v>
       </c>
       <c r="F204" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="G204" t="n">
-        <v>9</v>
+        <v>3</v>
       </c>
       <c r="H204" t="n">
         <v>2</v>
       </c>
       <c r="I204" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="J204" t="n">
+        <v>8</v>
+      </c>
+      <c r="K204" t="n">
         <v>2</v>
       </c>
     </row>
@@ -7886,18 +8501,21 @@
         <v>50</v>
       </c>
       <c r="F205" t="n">
-        <v>18</v>
+        <v>4</v>
       </c>
       <c r="G205" t="n">
-        <v>19</v>
+        <v>10</v>
       </c>
       <c r="H205" t="n">
-        <v>18</v>
+        <v>9</v>
       </c>
       <c r="I205" t="n">
-        <v>18</v>
+        <v>14</v>
       </c>
       <c r="J205" t="n">
+        <v>36</v>
+      </c>
+      <c r="K205" t="n">
         <v>17</v>
       </c>
     </row>
@@ -7922,18 +8540,21 @@
         <v>43</v>
       </c>
       <c r="F206" t="n">
-        <v>18</v>
+        <v>1</v>
       </c>
       <c r="G206" t="n">
-        <v>19</v>
+        <v>10</v>
       </c>
       <c r="H206" t="n">
-        <v>20</v>
+        <v>12</v>
       </c>
       <c r="I206" t="n">
-        <v>18</v>
+        <v>14</v>
       </c>
       <c r="J206" t="n">
+        <v>38</v>
+      </c>
+      <c r="K206" t="n">
         <v>7</v>
       </c>
     </row>
@@ -7958,18 +8579,21 @@
         <v>36</v>
       </c>
       <c r="F207" t="n">
-        <v>23</v>
+        <v>7</v>
       </c>
       <c r="G207" t="n">
-        <v>13</v>
+        <v>9</v>
       </c>
       <c r="H207" t="n">
-        <v>17</v>
+        <v>11</v>
       </c>
       <c r="I207" t="n">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="J207" t="n">
+        <v>29</v>
+      </c>
+      <c r="K207" t="n">
         <v>1</v>
       </c>
     </row>
@@ -7994,18 +8618,21 @@
         <v>22</v>
       </c>
       <c r="F208" t="n">
+        <v>4</v>
+      </c>
+      <c r="G208" t="n">
+        <v>4</v>
+      </c>
+      <c r="H208" t="n">
+        <v>6</v>
+      </c>
+      <c r="I208" t="n">
         <v>10</v>
       </c>
-      <c r="G208" t="n">
-        <v>14</v>
-      </c>
-      <c r="H208" t="n">
-        <v>9</v>
-      </c>
-      <c r="I208" t="n">
-        <v>16</v>
-      </c>
       <c r="J208" t="n">
+        <v>25</v>
+      </c>
+      <c r="K208" t="n">
         <v>0</v>
       </c>
     </row>
@@ -8030,18 +8657,21 @@
         <v>17</v>
       </c>
       <c r="F209" t="n">
-        <v>12</v>
+        <v>1</v>
       </c>
       <c r="G209" t="n">
         <v>8</v>
       </c>
       <c r="H209" t="n">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="I209" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="J209" t="n">
+        <v>15</v>
+      </c>
+      <c r="K209" t="n">
         <v>2</v>
       </c>
     </row>
@@ -8066,18 +8696,21 @@
         <v>20</v>
       </c>
       <c r="F210" t="n">
-        <v>10</v>
+        <v>2</v>
       </c>
       <c r="G210" t="n">
-        <v>12</v>
+        <v>7</v>
       </c>
       <c r="H210" t="n">
-        <v>9</v>
+        <v>2</v>
       </c>
       <c r="I210" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="J210" t="n">
+        <v>19</v>
+      </c>
+      <c r="K210" t="n">
         <v>1</v>
       </c>
     </row>
@@ -8102,18 +8735,21 @@
         <v>21</v>
       </c>
       <c r="F211" t="n">
-        <v>8</v>
+        <v>2</v>
       </c>
       <c r="G211" t="n">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="H211" t="n">
-        <v>11</v>
+        <v>4</v>
       </c>
       <c r="I211" t="n">
         <v>6</v>
       </c>
       <c r="J211" t="n">
+        <v>17</v>
+      </c>
+      <c r="K211" t="n">
         <v>4</v>
       </c>
     </row>
@@ -8138,18 +8774,21 @@
         <v>18</v>
       </c>
       <c r="F212" t="n">
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="G212" t="n">
-        <v>14</v>
+        <v>5</v>
       </c>
       <c r="H212" t="n">
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="I212" t="n">
-        <v>3</v>
+        <v>11</v>
       </c>
       <c r="J212" t="n">
+        <v>13</v>
+      </c>
+      <c r="K212" t="n">
         <v>0</v>
       </c>
     </row>
@@ -8174,18 +8813,21 @@
         <v>24</v>
       </c>
       <c r="F213" t="n">
-        <v>12</v>
+        <v>1</v>
       </c>
       <c r="G213" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="H213" t="n">
-        <v>15</v>
+        <v>5</v>
       </c>
       <c r="I213" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="J213" t="n">
+        <v>23</v>
+      </c>
+      <c r="K213" t="n">
         <v>0</v>
       </c>
     </row>
@@ -8210,18 +8852,21 @@
         <v>13</v>
       </c>
       <c r="F214" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="G214" t="n">
-        <v>11</v>
+        <v>2</v>
       </c>
       <c r="H214" t="n">
         <v>5</v>
       </c>
       <c r="I214" t="n">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="J214" t="n">
+        <v>9</v>
+      </c>
+      <c r="K214" t="n">
         <v>0</v>
       </c>
     </row>
@@ -8246,18 +8891,21 @@
         <v>21</v>
       </c>
       <c r="F215" t="n">
-        <v>14</v>
+        <v>3</v>
       </c>
       <c r="G215" t="n">
         <v>8</v>
       </c>
       <c r="H215" t="n">
-        <v>15</v>
+        <v>5</v>
       </c>
       <c r="I215" t="n">
-        <v>12</v>
+        <v>6</v>
       </c>
       <c r="J215" t="n">
+        <v>27</v>
+      </c>
+      <c r="K215" t="n">
         <v>1</v>
       </c>
     </row>
@@ -8288,12 +8936,15 @@
         <v>0</v>
       </c>
       <c r="H216" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I216" t="n">
         <v>0</v>
       </c>
       <c r="J216" t="n">
+        <v>1</v>
+      </c>
+      <c r="K216" t="n">
         <v>0</v>
       </c>
     </row>
@@ -8318,18 +8969,21 @@
         <v>66</v>
       </c>
       <c r="F217" t="n">
+        <v>4</v>
+      </c>
+      <c r="G217" t="n">
+        <v>15</v>
+      </c>
+      <c r="H217" t="n">
+        <v>17</v>
+      </c>
+      <c r="I217" t="n">
         <v>29</v>
       </c>
-      <c r="G217" t="n">
-        <v>36</v>
-      </c>
-      <c r="H217" t="n">
-        <v>24</v>
-      </c>
-      <c r="I217" t="n">
-        <v>34</v>
-      </c>
       <c r="J217" t="n">
+        <v>58</v>
+      </c>
+      <c r="K217" t="n">
         <v>4</v>
       </c>
     </row>
@@ -8354,18 +9008,21 @@
         <v>53</v>
       </c>
       <c r="F218" t="n">
-        <v>20</v>
+        <v>12</v>
       </c>
       <c r="G218" t="n">
+        <v>5</v>
+      </c>
+      <c r="H218" t="n">
+        <v>7</v>
+      </c>
+      <c r="I218" t="n">
+        <v>24</v>
+      </c>
+      <c r="J218" t="n">
         <v>28</v>
       </c>
-      <c r="H218" t="n">
-        <v>14</v>
-      </c>
-      <c r="I218" t="n">
-        <v>14</v>
-      </c>
-      <c r="J218" t="n">
+      <c r="K218" t="n">
         <v>8</v>
       </c>
     </row>
@@ -8390,18 +9047,21 @@
         <v>58</v>
       </c>
       <c r="F219" t="n">
-        <v>28</v>
+        <v>5</v>
       </c>
       <c r="G219" t="n">
-        <v>27</v>
+        <v>16</v>
       </c>
       <c r="H219" t="n">
-        <v>17</v>
+        <v>10</v>
       </c>
       <c r="I219" t="n">
-        <v>30</v>
+        <v>24</v>
       </c>
       <c r="J219" t="n">
+        <v>47</v>
+      </c>
+      <c r="K219" t="n">
         <v>5</v>
       </c>
     </row>
@@ -8426,18 +9086,21 @@
         <v>30</v>
       </c>
       <c r="F220" t="n">
+        <v>5</v>
+      </c>
+      <c r="G220" t="n">
+        <v>7</v>
+      </c>
+      <c r="H220" t="n">
+        <v>5</v>
+      </c>
+      <c r="I220" t="n">
         <v>13</v>
       </c>
-      <c r="G220" t="n">
-        <v>17</v>
-      </c>
-      <c r="H220" t="n">
-        <v>14</v>
-      </c>
-      <c r="I220" t="n">
-        <v>8</v>
-      </c>
       <c r="J220" t="n">
+        <v>22</v>
+      </c>
+      <c r="K220" t="n">
         <v>5</v>
       </c>
     </row>
@@ -8462,18 +9125,21 @@
         <v>72</v>
       </c>
       <c r="F221" t="n">
-        <v>30</v>
+        <v>10</v>
       </c>
       <c r="G221" t="n">
-        <v>34</v>
+        <v>13</v>
       </c>
       <c r="H221" t="n">
-        <v>32</v>
+        <v>15</v>
       </c>
       <c r="I221" t="n">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="J221" t="n">
+        <v>56</v>
+      </c>
+      <c r="K221" t="n">
         <v>15</v>
       </c>
     </row>
@@ -8498,18 +9164,21 @@
         <v>94</v>
       </c>
       <c r="F222" t="n">
-        <v>39</v>
+        <v>11</v>
       </c>
       <c r="G222" t="n">
-        <v>48</v>
+        <v>23</v>
       </c>
       <c r="H222" t="n">
-        <v>35</v>
+        <v>10</v>
       </c>
       <c r="I222" t="n">
-        <v>30</v>
+        <v>43</v>
       </c>
       <c r="J222" t="n">
+        <v>65</v>
+      </c>
+      <c r="K222" t="n">
         <v>18</v>
       </c>
     </row>
@@ -8534,18 +9203,21 @@
         <v>5</v>
       </c>
       <c r="F223" t="n">
+        <v>0</v>
+      </c>
+      <c r="G223" t="n">
+        <v>0</v>
+      </c>
+      <c r="H223" t="n">
+        <v>3</v>
+      </c>
+      <c r="I223" t="n">
         <v>1</v>
       </c>
-      <c r="G223" t="n">
-        <v>3</v>
-      </c>
-      <c r="H223" t="n">
-        <v>2</v>
-      </c>
-      <c r="I223" t="n">
-        <v>5</v>
-      </c>
       <c r="J223" t="n">
+        <v>7</v>
+      </c>
+      <c r="K223" t="n">
         <v>4</v>
       </c>
     </row>
@@ -8570,18 +9242,21 @@
         <v>38</v>
       </c>
       <c r="F224" t="n">
-        <v>9</v>
+        <v>1</v>
       </c>
       <c r="G224" t="n">
-        <v>17</v>
+        <v>4</v>
       </c>
       <c r="H224" t="n">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="I224" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="J224" t="n">
+        <v>26</v>
+      </c>
+      <c r="K224" t="n">
         <v>7</v>
       </c>
     </row>
@@ -8606,18 +9281,21 @@
         <v>37</v>
       </c>
       <c r="F225" t="n">
-        <v>15</v>
+        <v>3</v>
       </c>
       <c r="G225" t="n">
+        <v>7</v>
+      </c>
+      <c r="H225" t="n">
+        <v>5</v>
+      </c>
+      <c r="I225" t="n">
         <v>8</v>
       </c>
-      <c r="H225" t="n">
-        <v>14</v>
-      </c>
-      <c r="I225" t="n">
-        <v>9</v>
-      </c>
       <c r="J225" t="n">
+        <v>23</v>
+      </c>
+      <c r="K225" t="n">
         <v>14</v>
       </c>
     </row>
@@ -8642,18 +9320,21 @@
         <v>60</v>
       </c>
       <c r="F226" t="n">
-        <v>18</v>
+        <v>6</v>
       </c>
       <c r="G226" t="n">
-        <v>26</v>
+        <v>5</v>
       </c>
       <c r="H226" t="n">
-        <v>24</v>
+        <v>14</v>
       </c>
       <c r="I226" t="n">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="J226" t="n">
+        <v>45</v>
+      </c>
+      <c r="K226" t="n">
         <v>16</v>
       </c>
     </row>
@@ -8678,18 +9359,21 @@
         <v>65</v>
       </c>
       <c r="F227" t="n">
-        <v>21</v>
+        <v>4</v>
       </c>
       <c r="G227" t="n">
-        <v>26</v>
+        <v>11</v>
       </c>
       <c r="H227" t="n">
-        <v>19</v>
+        <v>10</v>
       </c>
       <c r="I227" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="J227" t="n">
+        <v>42</v>
+      </c>
+      <c r="K227" t="n">
         <v>14</v>
       </c>
     </row>
@@ -8717,17 +9401,20 @@
         <v>0</v>
       </c>
       <c r="G228" t="n">
+        <v>0</v>
+      </c>
+      <c r="H228" t="n">
+        <v>0</v>
+      </c>
+      <c r="I228" t="n">
         <v>1</v>
-      </c>
-      <c r="H228" t="n">
-        <v>1</v>
-      </c>
-      <c r="I228" t="n">
-        <v>0</v>
       </c>
       <c r="J228" t="n">
         <v>1</v>
       </c>
+      <c r="K228" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="229">
       <c r="A229" t="inlineStr">
@@ -8750,18 +9437,21 @@
         <v>69</v>
       </c>
       <c r="F229" t="n">
-        <v>26</v>
+        <v>4</v>
       </c>
       <c r="G229" t="n">
-        <v>33</v>
+        <v>14</v>
       </c>
       <c r="H229" t="n">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="I229" t="n">
-        <v>36</v>
+        <v>25</v>
       </c>
       <c r="J229" t="n">
+        <v>54</v>
+      </c>
+      <c r="K229" t="n">
         <v>14</v>
       </c>
     </row>
@@ -8786,18 +9476,21 @@
         <v>109</v>
       </c>
       <c r="F230" t="n">
-        <v>54</v>
+        <v>21</v>
       </c>
       <c r="G230" t="n">
-        <v>62</v>
+        <v>21</v>
       </c>
       <c r="H230" t="n">
-        <v>52</v>
+        <v>26</v>
       </c>
       <c r="I230" t="n">
-        <v>36</v>
+        <v>48</v>
       </c>
       <c r="J230" t="n">
+        <v>88</v>
+      </c>
+      <c r="K230" t="n">
         <v>18</v>
       </c>
     </row>
@@ -8822,18 +9515,21 @@
         <v>46</v>
       </c>
       <c r="F231" t="n">
-        <v>21</v>
+        <v>8</v>
       </c>
       <c r="G231" t="n">
-        <v>21</v>
+        <v>11</v>
       </c>
       <c r="H231" t="n">
-        <v>17</v>
+        <v>3</v>
       </c>
       <c r="I231" t="n">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="J231" t="n">
+        <v>35</v>
+      </c>
+      <c r="K231" t="n">
         <v>9</v>
       </c>
     </row>
@@ -8858,18 +9554,21 @@
         <v>15</v>
       </c>
       <c r="F232" t="n">
+        <v>3</v>
+      </c>
+      <c r="G232" t="n">
+        <v>3</v>
+      </c>
+      <c r="H232" t="n">
+        <v>1</v>
+      </c>
+      <c r="I232" t="n">
         <v>6</v>
       </c>
-      <c r="G232" t="n">
-        <v>7</v>
-      </c>
-      <c r="H232" t="n">
-        <v>9</v>
-      </c>
-      <c r="I232" t="n">
-        <v>4</v>
-      </c>
       <c r="J232" t="n">
+        <v>13</v>
+      </c>
+      <c r="K232" t="n">
         <v>1</v>
       </c>
     </row>
@@ -8894,18 +9593,21 @@
         <v>28</v>
       </c>
       <c r="F233" t="n">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="G233" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="H233" t="n">
-        <v>13</v>
+        <v>3</v>
       </c>
       <c r="I233" t="n">
-        <v>17</v>
+        <v>7</v>
       </c>
       <c r="J233" t="n">
+        <v>30</v>
+      </c>
+      <c r="K233" t="n">
         <v>9</v>
       </c>
     </row>
@@ -8930,18 +9632,21 @@
         <v>31</v>
       </c>
       <c r="F234" t="n">
-        <v>13</v>
+        <v>2</v>
       </c>
       <c r="G234" t="n">
+        <v>9</v>
+      </c>
+      <c r="H234" t="n">
+        <v>2</v>
+      </c>
+      <c r="I234" t="n">
         <v>15</v>
       </c>
-      <c r="H234" t="n">
-        <v>10</v>
-      </c>
-      <c r="I234" t="n">
-        <v>14</v>
-      </c>
       <c r="J234" t="n">
+        <v>24</v>
+      </c>
+      <c r="K234" t="n">
         <v>11</v>
       </c>
     </row>
@@ -8966,18 +9671,21 @@
         <v>34</v>
       </c>
       <c r="F235" t="n">
-        <v>20</v>
+        <v>8</v>
       </c>
       <c r="G235" t="n">
-        <v>16</v>
+        <v>7</v>
       </c>
       <c r="H235" t="n">
-        <v>19</v>
+        <v>7</v>
       </c>
       <c r="I235" t="n">
-        <v>3</v>
+        <v>14</v>
       </c>
       <c r="J235" t="n">
+        <v>22</v>
+      </c>
+      <c r="K235" t="n">
         <v>3</v>
       </c>
     </row>
@@ -9002,18 +9710,21 @@
         <v>12</v>
       </c>
       <c r="F236" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="G236" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="H236" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="I236" t="n">
         <v>5</v>
       </c>
       <c r="J236" t="n">
+        <v>11</v>
+      </c>
+      <c r="K236" t="n">
         <v>1</v>
       </c>
     </row>
@@ -9038,18 +9749,21 @@
         <v>17</v>
       </c>
       <c r="F237" t="n">
-        <v>11</v>
+        <v>2</v>
       </c>
       <c r="G237" t="n">
         <v>7</v>
       </c>
       <c r="H237" t="n">
-        <v>11</v>
+        <v>4</v>
       </c>
       <c r="I237" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="J237" t="n">
+        <v>15</v>
+      </c>
+      <c r="K237" t="n">
         <v>1</v>
       </c>
     </row>
@@ -9074,18 +9788,21 @@
         <v>15</v>
       </c>
       <c r="F238" t="n">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="G238" t="n">
-        <v>11</v>
+        <v>2</v>
       </c>
       <c r="H238" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="I238" t="n">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="J238" t="n">
+        <v>10</v>
+      </c>
+      <c r="K238" t="n">
         <v>3</v>
       </c>
     </row>
@@ -9110,18 +9827,21 @@
         <v>28</v>
       </c>
       <c r="F239" t="n">
+        <v>8</v>
+      </c>
+      <c r="G239" t="n">
+        <v>6</v>
+      </c>
+      <c r="H239" t="n">
+        <v>4</v>
+      </c>
+      <c r="I239" t="n">
+        <v>15</v>
+      </c>
+      <c r="J239" t="n">
         <v>17</v>
       </c>
-      <c r="G239" t="n">
-        <v>16</v>
-      </c>
-      <c r="H239" t="n">
-        <v>8</v>
-      </c>
-      <c r="I239" t="n">
-        <v>9</v>
-      </c>
-      <c r="J239" t="n">
+      <c r="K239" t="n">
         <v>4</v>
       </c>
     </row>
@@ -9146,18 +9866,21 @@
         <v>49</v>
       </c>
       <c r="F240" t="n">
-        <v>26</v>
+        <v>9</v>
       </c>
       <c r="G240" t="n">
+        <v>14</v>
+      </c>
+      <c r="H240" t="n">
+        <v>8</v>
+      </c>
+      <c r="I240" t="n">
+        <v>25</v>
+      </c>
+      <c r="J240" t="n">
         <v>30</v>
       </c>
-      <c r="H240" t="n">
-        <v>17</v>
-      </c>
-      <c r="I240" t="n">
-        <v>13</v>
-      </c>
-      <c r="J240" t="n">
+      <c r="K240" t="n">
         <v>3</v>
       </c>
     </row>
@@ -9182,18 +9905,21 @@
         <v>16</v>
       </c>
       <c r="F241" t="n">
+        <v>3</v>
+      </c>
+      <c r="G241" t="n">
+        <v>2</v>
+      </c>
+      <c r="H241" t="n">
         <v>6</v>
       </c>
-      <c r="G241" t="n">
-        <v>10</v>
-      </c>
-      <c r="H241" t="n">
-        <v>7</v>
-      </c>
       <c r="I241" t="n">
-        <v>11</v>
+        <v>5</v>
       </c>
       <c r="J241" t="n">
+        <v>18</v>
+      </c>
+      <c r="K241" t="n">
         <v>3</v>
       </c>
     </row>
@@ -9218,18 +9944,21 @@
         <v>53</v>
       </c>
       <c r="F242" t="n">
-        <v>27</v>
+        <v>6</v>
       </c>
       <c r="G242" t="n">
-        <v>28</v>
+        <v>12</v>
       </c>
       <c r="H242" t="n">
-        <v>28</v>
+        <v>17</v>
       </c>
       <c r="I242" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="J242" t="n">
+        <v>49</v>
+      </c>
+      <c r="K242" t="n">
         <v>13</v>
       </c>
     </row>
@@ -9254,18 +9983,21 @@
         <v>56</v>
       </c>
       <c r="F243" t="n">
-        <v>21</v>
+        <v>4</v>
       </c>
       <c r="G243" t="n">
-        <v>18</v>
+        <v>11</v>
       </c>
       <c r="H243" t="n">
-        <v>27</v>
+        <v>10</v>
       </c>
       <c r="I243" t="n">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="J243" t="n">
+        <v>38</v>
+      </c>
+      <c r="K243" t="n">
         <v>15</v>
       </c>
     </row>
@@ -9290,18 +10022,21 @@
         <v>8</v>
       </c>
       <c r="F244" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="G244" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="H244" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="I244" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="J244" t="n">
+        <v>6</v>
+      </c>
+      <c r="K244" t="n">
         <v>1</v>
       </c>
     </row>
@@ -9326,18 +10061,21 @@
         <v>43</v>
       </c>
       <c r="F245" t="n">
-        <v>23</v>
+        <v>8</v>
       </c>
       <c r="G245" t="n">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="H245" t="n">
-        <v>34</v>
+        <v>8</v>
       </c>
       <c r="I245" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="J245" t="n">
+        <v>42</v>
+      </c>
+      <c r="K245" t="n">
         <v>6</v>
       </c>
     </row>
@@ -9362,18 +10100,21 @@
         <v>42</v>
       </c>
       <c r="F246" t="n">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="G246" t="n">
-        <v>16</v>
+        <v>8</v>
       </c>
       <c r="H246" t="n">
+        <v>3</v>
+      </c>
+      <c r="I246" t="n">
         <v>15</v>
       </c>
-      <c r="I246" t="n">
-        <v>22</v>
-      </c>
       <c r="J246" t="n">
+        <v>37</v>
+      </c>
+      <c r="K246" t="n">
         <v>7</v>
       </c>
     </row>
@@ -9398,18 +10139,21 @@
         <v>42</v>
       </c>
       <c r="F247" t="n">
-        <v>14</v>
+        <v>5</v>
       </c>
       <c r="G247" t="n">
-        <v>25</v>
+        <v>8</v>
       </c>
       <c r="H247" t="n">
-        <v>21</v>
+        <v>7</v>
       </c>
       <c r="I247" t="n">
-        <v>11</v>
+        <v>19</v>
       </c>
       <c r="J247" t="n">
+        <v>32</v>
+      </c>
+      <c r="K247" t="n">
         <v>10</v>
       </c>
     </row>
@@ -9434,18 +10178,21 @@
         <v>43</v>
       </c>
       <c r="F248" t="n">
-        <v>18</v>
+        <v>7</v>
       </c>
       <c r="G248" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="H248" t="n">
-        <v>18</v>
+        <v>5</v>
       </c>
       <c r="I248" t="n">
-        <v>18</v>
+        <v>7</v>
       </c>
       <c r="J248" t="n">
+        <v>36</v>
+      </c>
+      <c r="K248" t="n">
         <v>17</v>
       </c>
     </row>
@@ -9470,18 +10217,21 @@
         <v>67</v>
       </c>
       <c r="F249" t="n">
-        <v>30</v>
+        <v>10</v>
       </c>
       <c r="G249" t="n">
-        <v>30</v>
+        <v>15</v>
       </c>
       <c r="H249" t="n">
-        <v>29</v>
+        <v>14</v>
       </c>
       <c r="I249" t="n">
-        <v>18</v>
+        <v>21</v>
       </c>
       <c r="J249" t="n">
+        <v>47</v>
+      </c>
+      <c r="K249" t="n">
         <v>10</v>
       </c>
     </row>
@@ -9506,18 +10256,21 @@
         <v>60</v>
       </c>
       <c r="F250" t="n">
+        <v>7</v>
+      </c>
+      <c r="G250" t="n">
+        <v>8</v>
+      </c>
+      <c r="H250" t="n">
+        <v>15</v>
+      </c>
+      <c r="I250" t="n">
         <v>22</v>
       </c>
-      <c r="G250" t="n">
-        <v>30</v>
-      </c>
-      <c r="H250" t="n">
-        <v>25</v>
-      </c>
-      <c r="I250" t="n">
-        <v>20</v>
-      </c>
       <c r="J250" t="n">
+        <v>45</v>
+      </c>
+      <c r="K250" t="n">
         <v>8</v>
       </c>
     </row>
@@ -9542,18 +10295,21 @@
         <v>44</v>
       </c>
       <c r="F251" t="n">
-        <v>12</v>
+        <v>3</v>
       </c>
       <c r="G251" t="n">
-        <v>20</v>
+        <v>7</v>
       </c>
       <c r="H251" t="n">
+        <v>5</v>
+      </c>
+      <c r="I251" t="n">
         <v>17</v>
       </c>
-      <c r="I251" t="n">
-        <v>19</v>
-      </c>
       <c r="J251" t="n">
+        <v>36</v>
+      </c>
+      <c r="K251" t="n">
         <v>10</v>
       </c>
     </row>
@@ -9578,18 +10334,21 @@
         <v>43</v>
       </c>
       <c r="F252" t="n">
-        <v>20</v>
+        <v>5</v>
       </c>
       <c r="G252" t="n">
-        <v>16</v>
+        <v>9</v>
       </c>
       <c r="H252" t="n">
-        <v>22</v>
+        <v>13</v>
       </c>
       <c r="I252" t="n">
-        <v>16</v>
+        <v>9</v>
       </c>
       <c r="J252" t="n">
+        <v>38</v>
+      </c>
+      <c r="K252" t="n">
         <v>13</v>
       </c>
     </row>
@@ -9614,18 +10373,21 @@
         <v>43</v>
       </c>
       <c r="F253" t="n">
-        <v>19</v>
+        <v>5</v>
       </c>
       <c r="G253" t="n">
-        <v>15</v>
+        <v>7</v>
       </c>
       <c r="H253" t="n">
-        <v>17</v>
+        <v>8</v>
       </c>
       <c r="I253" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="J253" t="n">
+        <v>32</v>
+      </c>
+      <c r="K253" t="n">
         <v>14</v>
       </c>
     </row>
@@ -9650,18 +10412,21 @@
         <v>73</v>
       </c>
       <c r="F254" t="n">
-        <v>21</v>
+        <v>7</v>
       </c>
       <c r="G254" t="n">
-        <v>35</v>
+        <v>10</v>
       </c>
       <c r="H254" t="n">
-        <v>31</v>
+        <v>10</v>
       </c>
       <c r="I254" t="n">
-        <v>31</v>
+        <v>29</v>
       </c>
       <c r="J254" t="n">
+        <v>62</v>
+      </c>
+      <c r="K254" t="n">
         <v>13</v>
       </c>
     </row>
@@ -9686,18 +10451,21 @@
         <v>31</v>
       </c>
       <c r="F255" t="n">
-        <v>20</v>
+        <v>7</v>
       </c>
       <c r="G255" t="n">
-        <v>23</v>
+        <v>9</v>
       </c>
       <c r="H255" t="n">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="I255" t="n">
-        <v>5</v>
+        <v>19</v>
       </c>
       <c r="J255" t="n">
+        <v>17</v>
+      </c>
+      <c r="K255" t="n">
         <v>6</v>
       </c>
     </row>
@@ -9722,18 +10490,21 @@
         <v>64</v>
       </c>
       <c r="F256" t="n">
-        <v>38</v>
+        <v>11</v>
       </c>
       <c r="G256" t="n">
-        <v>28</v>
+        <v>19</v>
       </c>
       <c r="H256" t="n">
+        <v>11</v>
+      </c>
+      <c r="I256" t="n">
         <v>25</v>
       </c>
-      <c r="I256" t="n">
-        <v>21</v>
-      </c>
       <c r="J256" t="n">
+        <v>46</v>
+      </c>
+      <c r="K256" t="n">
         <v>11</v>
       </c>
     </row>
@@ -9758,18 +10529,21 @@
         <v>33</v>
       </c>
       <c r="F257" t="n">
-        <v>20</v>
+        <v>5</v>
       </c>
       <c r="G257" t="n">
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="H257" t="n">
-        <v>15</v>
+        <v>5</v>
       </c>
       <c r="I257" t="n">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="J257" t="n">
+        <v>25</v>
+      </c>
+      <c r="K257" t="n">
         <v>3</v>
       </c>
     </row>
@@ -9794,18 +10568,21 @@
         <v>30</v>
       </c>
       <c r="F258" t="n">
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="G258" t="n">
-        <v>18</v>
+        <v>5</v>
       </c>
       <c r="H258" t="n">
-        <v>17</v>
+        <v>4</v>
       </c>
       <c r="I258" t="n">
-        <v>6</v>
+        <v>15</v>
       </c>
       <c r="J258" t="n">
+        <v>23</v>
+      </c>
+      <c r="K258" t="n">
         <v>3</v>
       </c>
     </row>
@@ -9830,18 +10607,21 @@
         <v>13</v>
       </c>
       <c r="F259" t="n">
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="G259" t="n">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="H259" t="n">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="I259" t="n">
         <v>7</v>
       </c>
       <c r="J259" t="n">
+        <v>14</v>
+      </c>
+      <c r="K259" t="n">
         <v>1</v>
       </c>
     </row>
@@ -9866,18 +10646,21 @@
         <v>36</v>
       </c>
       <c r="F260" t="n">
-        <v>18</v>
+        <v>5</v>
       </c>
       <c r="G260" t="n">
-        <v>20</v>
+        <v>6</v>
       </c>
       <c r="H260" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="I260" t="n">
-        <v>12</v>
+        <v>17</v>
       </c>
       <c r="J260" t="n">
+        <v>27</v>
+      </c>
+      <c r="K260" t="n">
         <v>5</v>
       </c>
     </row>
@@ -9902,18 +10685,21 @@
         <v>36</v>
       </c>
       <c r="F261" t="n">
-        <v>11</v>
+        <v>5</v>
       </c>
       <c r="G261" t="n">
-        <v>19</v>
+        <v>3</v>
       </c>
       <c r="H261" t="n">
-        <v>16</v>
+        <v>9</v>
       </c>
       <c r="I261" t="n">
-        <v>20</v>
+        <v>13</v>
       </c>
       <c r="J261" t="n">
+        <v>36</v>
+      </c>
+      <c r="K261" t="n">
         <v>4</v>
       </c>
     </row>
@@ -9938,18 +10724,21 @@
         <v>24</v>
       </c>
       <c r="F262" t="n">
-        <v>11</v>
+        <v>3</v>
       </c>
       <c r="G262" t="n">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="H262" t="n">
-        <v>11</v>
+        <v>3</v>
       </c>
       <c r="I262" t="n">
-        <v>4</v>
+        <v>9</v>
       </c>
       <c r="J262" t="n">
+        <v>15</v>
+      </c>
+      <c r="K262" t="n">
         <v>4</v>
       </c>
     </row>
@@ -9974,18 +10763,21 @@
         <v>11</v>
       </c>
       <c r="F263" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="G263" t="n">
+        <v>1</v>
+      </c>
+      <c r="H263" t="n">
+        <v>1</v>
+      </c>
+      <c r="I263" t="n">
         <v>8</v>
       </c>
-      <c r="H263" t="n">
-        <v>4</v>
-      </c>
-      <c r="I263" t="n">
-        <v>5</v>
-      </c>
       <c r="J263" t="n">
+        <v>9</v>
+      </c>
+      <c r="K263" t="n">
         <v>3</v>
       </c>
     </row>
@@ -10010,18 +10802,21 @@
         <v>39</v>
       </c>
       <c r="F264" t="n">
-        <v>13</v>
+        <v>5</v>
       </c>
       <c r="G264" t="n">
-        <v>26</v>
+        <v>7</v>
       </c>
       <c r="H264" t="n">
-        <v>15</v>
+        <v>8</v>
       </c>
       <c r="I264" t="n">
-        <v>24</v>
+        <v>19</v>
       </c>
       <c r="J264" t="n">
+        <v>39</v>
+      </c>
+      <c r="K264" t="n">
         <v>13</v>
       </c>
     </row>
@@ -10046,18 +10841,21 @@
         <v>57</v>
       </c>
       <c r="F265" t="n">
-        <v>21</v>
+        <v>10</v>
       </c>
       <c r="G265" t="n">
-        <v>30</v>
+        <v>10</v>
       </c>
       <c r="H265" t="n">
-        <v>23</v>
+        <v>6</v>
       </c>
       <c r="I265" t="n">
-        <v>20</v>
+        <v>25</v>
       </c>
       <c r="J265" t="n">
+        <v>43</v>
+      </c>
+      <c r="K265" t="n">
         <v>17</v>
       </c>
     </row>
@@ -10082,18 +10880,21 @@
         <v>25</v>
       </c>
       <c r="F266" t="n">
-        <v>15</v>
+        <v>4</v>
       </c>
       <c r="G266" t="n">
+        <v>8</v>
+      </c>
+      <c r="H266" t="n">
+        <v>3</v>
+      </c>
+      <c r="I266" t="n">
         <v>9</v>
       </c>
-      <c r="H266" t="n">
-        <v>17</v>
-      </c>
-      <c r="I266" t="n">
-        <v>10</v>
-      </c>
       <c r="J266" t="n">
+        <v>27</v>
+      </c>
+      <c r="K266" t="n">
         <v>2</v>
       </c>
     </row>
@@ -10118,23 +10919,26 @@
         <v>23</v>
       </c>
       <c r="F267" t="n">
-        <v>8</v>
+        <v>2</v>
       </c>
       <c r="G267" t="n">
-        <v>13</v>
+        <v>5</v>
       </c>
       <c r="H267" t="n">
-        <v>12</v>
+        <v>4</v>
       </c>
       <c r="I267" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="J267" t="n">
+        <v>20</v>
+      </c>
+      <c r="K267" t="n">
         <v>4</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:J1"/>
+  <autoFilter ref="A1:K1"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>